--- a/tiflow-bfarm/fhir-error-codes/1.0.0-draft/StructureDefinition-erp-tprescription-medication.xlsx
+++ b/tiflow-bfarm/fhir-error-codes/1.0.0-draft/StructureDefinition-erp-tprescription-medication.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7288" uniqueCount="713">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7294" uniqueCount="717">
   <si>
     <t>Property</t>
   </si>
@@ -442,7 +442,7 @@
     <t>Medication.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
+    <t xml:space="preserve">canonical(StructureDefinition)
 </t>
   </si>
   <si>
@@ -480,7 +480,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -514,7 +514,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -557,7 +557,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -592,6 +592,10 @@
     <t>Medication.contained</t>
   </si>
   <si>
+    <t>inline resources
+anonymous resourcescontained resources</t>
+  </si>
+  <si>
     <t xml:space="preserve">Medication {https://gematik.de/fhir/epa-medication/StructureDefinition/epa-medication-pharmaceutical-product|https://gematik.de/fhir/epa-medication/StructureDefinition/epa-medication-pzn-ingredient}
 </t>
   </si>
@@ -599,12 +603,18 @@
     <t>Enthaltene Medikationen</t>
   </si>
   <si>
+    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+  </si>
+  <si>
     <t>Im Falle einer Rezeptur oder Kombipackung sind die Bestandteile der Rezeptur, bzw. Kombipackung hier als Medications gelistet.</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>Medication.extension</t>
   </si>
   <si>
@@ -612,9 +622,6 @@
   </si>
   <si>
     <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>N/A</t>
   </si>
   <si>
     <t>Medication.extension:rxPrescriptionProcessIdentifier</t>
@@ -627,7 +634,7 @@
 </t>
   </si>
   <si>
-    <t>Extension</t>
+    <t>Optional Extensions Element</t>
   </si>
   <si>
     <t>This extension is used to track medication prescription transactions between the E-Rezept-Fachdienst and the ePA. The RxPrescriptionProcessIdentifier is generated by the ePA Medication Service and consists of the PrescriptionId and the authoredOn date of the operation parameters request. It ensures consistent referencing and management of medication-related resources across different systems.</t>
@@ -656,6 +663,9 @@
   </si>
   <si>
     <t>Medication.extension.extension</t>
+  </si>
+  <si>
+    <t>Extension</t>
   </si>
   <si>
     <t>An Extension</t>
@@ -1060,6 +1070,12 @@
 </t>
   </si>
   <si>
+    <t>An identifier intended for computation</t>
+  </si>
+  <si>
+    <t>An identifier - identifies some entity uniquely and unambiguously. Typically this is used for business identifiers.</t>
+  </si>
+  <si>
     <t>&lt;valueIdentifier xmlns="http://hl7.org/fhir"&gt;
   &lt;system value="https://gematik.de/fhir/epa-medication/sid/epa-medication-unique-identifier"/&gt;
 &lt;/valueIdentifier&gt;</t>
@@ -1099,7 +1115,7 @@
     <t>A coded concept that defines the type of a medication.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-codes|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-codes</t>
   </si>
   <si>
     <t>coding.code = //element(*,MedicationType)/DrugCoded/ProductCode@@ -1319,7 +1335,7 @@
     <t>Medication.manufacturer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1)
+    <t xml:space="preserve">Reference(Organization)
 </t>
   </si>
   <si>
@@ -1389,7 +1405,7 @@
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
   </si>
   <si>
     <t>Reference.type</t>
@@ -1446,7 +1462,7 @@
     <t>A coded concept defining the form of a medication.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-form-codes|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-form-codes</t>
   </si>
   <si>
     <t>coding.code =  //element(*,DrugCodedType)/FormCode@@ -1896,7 +1912,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(Substance|4.0.1|Medication|4.0.1)</t>
+Reference(Substance|Medication)</t>
   </si>
   <si>
     <t>The actual ingredient or content</t>
@@ -1910,9 +1926,6 @@
   <si>
     <t xml:space="preserve">type:$this}
 </t>
-  </si>
-  <si>
-    <t>closed</t>
   </si>
   <si>
     <t>.player</t>
@@ -2563,7 +2576,7 @@
     <col min="1" max="1" width="64.22265625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="45.42578125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="25.1328125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="18.19140625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
@@ -4322,7 +4335,7 @@
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>77</v>
+        <v>183</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -4341,16 +4354,16 @@
         <v>77</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>82</v>
+        <v>186</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4400,7 +4413,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -4415,10 +4428,10 @@
         <v>77</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>85</v>
+        <v>189</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>77</v>
@@ -4429,10 +4442,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4461,7 +4474,7 @@
         <v>109</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="N17" t="s" s="2">
         <v>111</v>
@@ -4514,7 +4527,7 @@
         <v>114</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -4532,7 +4545,7 @@
         <v>77</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>77</v>
@@ -4543,13 +4556,13 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D18" t="s" s="2">
         <v>77</v>
@@ -4571,13 +4584,13 @@
         <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4628,7 +4641,7 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -4637,7 +4650,7 @@
         <v>79</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="AJ18" t="s" s="2">
         <v>116</v>
@@ -4646,7 +4659,7 @@
         <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>77</v>
+        <v>189</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>77</v>
@@ -4657,13 +4670,13 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>77</v>
@@ -4685,13 +4698,13 @@
         <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4742,7 +4755,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -4751,7 +4764,7 @@
         <v>79</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>116</v>
@@ -4760,7 +4773,7 @@
         <v>77</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>77</v>
+        <v>189</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>77</v>
@@ -4771,10 +4784,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4883,10 +4896,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4912,10 +4925,10 @@
         <v>108</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4995,10 +5008,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5024,13 +5037,13 @@
         <v>129</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -5038,7 +5051,7 @@
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>77</v>
@@ -5080,7 +5093,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>87</v>
@@ -5098,7 +5111,7 @@
         <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>77</v>
@@ -5109,10 +5122,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5135,13 +5148,13 @@
         <v>77</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -5192,7 +5205,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -5210,7 +5223,7 @@
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>77</v>
@@ -5221,13 +5234,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>77</v>
@@ -5249,13 +5262,13 @@
         <v>77</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -5306,7 +5319,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -5315,7 +5328,7 @@
         <v>79</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>116</v>
@@ -5324,7 +5337,7 @@
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>77</v>
+        <v>189</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>77</v>
@@ -5335,10 +5348,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5447,10 +5460,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5476,10 +5489,10 @@
         <v>108</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5559,10 +5572,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5588,13 +5601,13 @@
         <v>129</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5602,7 +5615,7 @@
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="S27" t="s" s="2">
         <v>77</v>
@@ -5644,7 +5657,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>87</v>
@@ -5662,7 +5675,7 @@
         <v>77</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>77</v>
@@ -5673,10 +5686,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5702,10 +5715,10 @@
         <v>141</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5732,11 +5745,11 @@
         <v>77</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Y28" s="2"/>
       <c r="Z28" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>77</v>
@@ -5754,7 +5767,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5772,7 +5785,7 @@
         <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
@@ -5783,10 +5796,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5895,10 +5908,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6009,10 +6022,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6038,16 +6051,16 @@
         <v>129</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>77</v>
@@ -6096,7 +6109,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -6114,21 +6127,21 @@
         <v>77</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6154,13 +6167,13 @@
         <v>101</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6210,7 +6223,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -6228,21 +6241,21 @@
         <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6268,14 +6281,14 @@
         <v>166</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -6324,7 +6337,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -6342,21 +6355,21 @@
         <v>77</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6382,16 +6395,16 @@
         <v>101</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -6440,7 +6453,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -6458,21 +6471,21 @@
         <v>77</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6495,19 +6508,19 @@
         <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -6556,7 +6569,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -6574,27 +6587,27 @@
         <v>77</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="D36" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -6613,15 +6626,17 @@
         <v>77</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>285</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -6670,7 +6685,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6679,7 +6694,7 @@
         <v>79</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>116</v>
@@ -6688,7 +6703,7 @@
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>190</v>
+        <v>105</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>77</v>
@@ -6699,10 +6714,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6811,10 +6826,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6925,10 +6940,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6954,13 +6969,13 @@
         <v>129</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6968,7 +6983,7 @@
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="S39" t="s" s="2">
         <v>77</v>
@@ -7010,7 +7025,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>87</v>
@@ -7028,7 +7043,7 @@
         <v>77</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>77</v>
@@ -7039,10 +7054,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7068,10 +7083,10 @@
         <v>166</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -7098,11 +7113,11 @@
         <v>77</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>77</v>
@@ -7120,7 +7135,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -7138,7 +7153,7 @@
         <v>77</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>77</v>
@@ -7149,16 +7164,16 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7177,15 +7192,17 @@
         <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>295</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>77</v>
@@ -7234,7 +7251,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -7243,7 +7260,7 @@
         <v>79</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>116</v>
@@ -7252,7 +7269,7 @@
         <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>77</v>
+        <v>189</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
@@ -7263,10 +7280,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7375,10 +7392,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7404,10 +7421,10 @@
         <v>108</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7487,10 +7504,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7516,13 +7533,13 @@
         <v>129</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7530,7 +7547,7 @@
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="S44" t="s" s="2">
         <v>77</v>
@@ -7572,7 +7589,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>87</v>
@@ -7590,7 +7607,7 @@
         <v>77</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>77</v>
@@ -7601,10 +7618,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7630,10 +7647,10 @@
         <v>101</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7657,7 +7674,7 @@
         <v>77</v>
       </c>
       <c r="W45" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="X45" t="s" s="2">
         <v>77</v>
@@ -7684,7 +7701,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7702,7 +7719,7 @@
         <v>77</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>77</v>
@@ -7713,13 +7730,13 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="D46" t="s" s="2">
         <v>77</v>
@@ -7741,13 +7758,13 @@
         <v>77</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7798,7 +7815,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7807,7 +7824,7 @@
         <v>79</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>116</v>
@@ -7816,7 +7833,7 @@
         <v>77</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>77</v>
+        <v>189</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>77</v>
@@ -7827,10 +7844,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7939,10 +7956,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7968,10 +7985,10 @@
         <v>108</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -8051,10 +8068,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8080,13 +8097,13 @@
         <v>129</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8094,7 +8111,7 @@
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="S49" t="s" s="2">
         <v>77</v>
@@ -8136,7 +8153,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>87</v>
@@ -8154,7 +8171,7 @@
         <v>77</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>77</v>
@@ -8165,10 +8182,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8194,10 +8211,10 @@
         <v>101</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8221,7 +8238,7 @@
         <v>77</v>
       </c>
       <c r="W50" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="X50" t="s" s="2">
         <v>77</v>
@@ -8248,7 +8265,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -8266,7 +8283,7 @@
         <v>77</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>77</v>
@@ -8277,13 +8294,13 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>77</v>
@@ -8305,13 +8322,13 @@
         <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8362,7 +8379,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -8371,7 +8388,7 @@
         <v>79</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>116</v>
@@ -8380,7 +8397,7 @@
         <v>77</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>77</v>
+        <v>189</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>77</v>
@@ -8391,10 +8408,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8420,16 +8437,16 @@
         <v>108</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="N52" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -8478,7 +8495,7 @@
         <v>114</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8496,7 +8513,7 @@
         <v>77</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>77</v>
@@ -8507,10 +8524,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8533,16 +8550,16 @@
         <v>88</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8580,7 +8597,7 @@
         <v>77</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="AC53" s="2"/>
       <c r="AD53" t="s" s="2">
@@ -8590,7 +8607,7 @@
         <v>114</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8608,24 +8625,24 @@
         <v>77</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>77</v>
@@ -8647,16 +8664,16 @@
         <v>88</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>324</v>
+        <v>337</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>325</v>
+        <v>338</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8667,7 +8684,7 @@
         <v>77</v>
       </c>
       <c r="S54" t="s" s="2">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="T54" t="s" s="2">
         <v>77</v>
@@ -8706,7 +8723,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8724,24 +8741,24 @@
         <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="D55" t="s" s="2">
         <v>77</v>
@@ -8763,16 +8780,16 @@
         <v>88</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="L55" t="s" s="2">
-        <v>324</v>
-      </c>
       <c r="M55" t="s" s="2">
-        <v>325</v>
+        <v>338</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8783,7 +8800,7 @@
         <v>77</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="T55" t="s" s="2">
         <v>77</v>
@@ -8822,7 +8839,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8840,21 +8857,21 @@
         <v>77</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8877,16 +8894,16 @@
         <v>88</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8915,28 +8932,28 @@
         <v>156</v>
       </c>
       <c r="Y56" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF56" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="Z56" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="AA56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF56" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8951,24 +8968,24 @@
         <v>99</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>349</v>
+        <v>354</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9077,10 +9094,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9191,10 +9208,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9220,16 +9237,16 @@
         <v>141</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>77</v>
@@ -9266,7 +9283,7 @@
         <v>77</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="AC59" s="2"/>
       <c r="AD59" t="s" s="2">
@@ -9276,7 +9293,7 @@
         <v>114</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -9294,24 +9311,24 @@
         <v>77</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>359</v>
+        <v>364</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="D60" t="s" s="2">
         <v>77</v>
@@ -9336,16 +9353,16 @@
         <v>141</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>77</v>
@@ -9355,46 +9372,46 @@
         <v>77</v>
       </c>
       <c r="S60" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF60" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="T60" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U60" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V60" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W60" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X60" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z60" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -9412,21 +9429,21 @@
         <v>77</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>359</v>
+        <v>364</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9535,10 +9552,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9649,10 +9666,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9678,16 +9695,16 @@
         <v>129</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>77</v>
@@ -9736,7 +9753,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9754,21 +9771,21 @@
         <v>77</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9794,13 +9811,13 @@
         <v>101</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9850,7 +9867,7 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9868,21 +9885,21 @@
         <v>77</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9908,14 +9925,14 @@
         <v>166</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>77</v>
@@ -9964,7 +9981,7 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9982,21 +9999,21 @@
         <v>77</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10022,16 +10039,16 @@
         <v>101</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>77</v>
@@ -10080,7 +10097,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -10098,21 +10115,21 @@
         <v>77</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10135,19 +10152,19 @@
         <v>88</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>77</v>
@@ -10196,7 +10213,7 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -10214,24 +10231,24 @@
         <v>77</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="D68" t="s" s="2">
         <v>77</v>
@@ -10256,16 +10273,16 @@
         <v>141</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>77</v>
@@ -10275,7 +10292,7 @@
         <v>77</v>
       </c>
       <c r="S68" t="s" s="2">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="T68" t="s" s="2">
         <v>77</v>
@@ -10314,7 +10331,7 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -10332,21 +10349,21 @@
         <v>77</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>359</v>
+        <v>364</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10455,10 +10472,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10569,10 +10586,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10598,16 +10615,16 @@
         <v>129</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>77</v>
@@ -10656,7 +10673,7 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10674,21 +10691,21 @@
         <v>77</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10714,13 +10731,13 @@
         <v>101</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10770,7 +10787,7 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10788,21 +10805,21 @@
         <v>77</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10828,14 +10845,14 @@
         <v>166</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>77</v>
@@ -10884,7 +10901,7 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10902,21 +10919,21 @@
         <v>77</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10942,16 +10959,16 @@
         <v>101</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>77</v>
@@ -11000,7 +11017,7 @@
         <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -11018,21 +11035,21 @@
         <v>77</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11055,19 +11072,19 @@
         <v>88</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>77</v>
@@ -11116,7 +11133,7 @@
         <v>77</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -11134,24 +11151,24 @@
         <v>77</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="D76" t="s" s="2">
         <v>77</v>
@@ -11176,16 +11193,16 @@
         <v>141</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>77</v>
@@ -11195,7 +11212,7 @@
         <v>77</v>
       </c>
       <c r="S76" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="T76" t="s" s="2">
         <v>77</v>
@@ -11234,7 +11251,7 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -11252,21 +11269,21 @@
         <v>77</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>359</v>
+        <v>364</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11375,10 +11392,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11489,10 +11506,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11518,16 +11535,16 @@
         <v>129</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>77</v>
@@ -11576,7 +11593,7 @@
         <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11594,21 +11611,21 @@
         <v>77</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11634,13 +11651,13 @@
         <v>101</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11690,7 +11707,7 @@
         <v>77</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -11708,21 +11725,21 @@
         <v>77</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11748,14 +11765,14 @@
         <v>166</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>77</v>
@@ -11804,7 +11821,7 @@
         <v>77</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -11822,21 +11839,21 @@
         <v>77</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11862,16 +11879,16 @@
         <v>101</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>77</v>
@@ -11920,7 +11937,7 @@
         <v>77</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -11938,21 +11955,21 @@
         <v>77</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11975,19 +11992,19 @@
         <v>88</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>77</v>
@@ -12036,7 +12053,7 @@
         <v>77</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -12054,21 +12071,21 @@
         <v>77</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12094,16 +12111,16 @@
         <v>101</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>77</v>
@@ -12152,7 +12169,7 @@
         <v>77</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -12170,21 +12187,21 @@
         <v>77</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>406</v>
+        <v>411</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12210,13 +12227,13 @@
         <v>166</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12242,31 +12259,31 @@
         <v>77</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="Z85" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF85" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="AA85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF85" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -12284,7 +12301,7 @@
         <v>77</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>77</v>
@@ -12295,10 +12312,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12321,16 +12338,16 @@
         <v>88</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12380,7 +12397,7 @@
         <v>77</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -12392,27 +12409,27 @@
         <v>149</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>423</v>
+        <v>428</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12521,10 +12538,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12635,10 +12652,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12664,13 +12681,13 @@
         <v>101</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -12720,7 +12737,7 @@
         <v>77</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -12729,7 +12746,7 @@
         <v>87</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="AJ89" t="s" s="2">
         <v>99</v>
@@ -12738,7 +12755,7 @@
         <v>77</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>77</v>
@@ -12749,10 +12766,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12778,13 +12795,13 @@
         <v>129</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -12813,10 +12830,10 @@
         <v>145</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>77</v>
@@ -12834,7 +12851,7 @@
         <v>77</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -12852,7 +12869,7 @@
         <v>77</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>77</v>
@@ -12863,10 +12880,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12889,16 +12906,16 @@
         <v>88</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -12948,7 +12965,7 @@
         <v>77</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -12966,21 +12983,21 @@
         <v>77</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13006,13 +13023,13 @@
         <v>101</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13062,7 +13079,7 @@
         <v>77</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -13080,7 +13097,7 @@
         <v>77</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>77</v>
@@ -13091,10 +13108,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13117,16 +13134,16 @@
         <v>77</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13155,28 +13172,28 @@
         <v>156</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="Z93" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF93" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="AA93" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB93" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC93" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD93" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE93" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF93" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -13191,24 +13208,24 @@
         <v>99</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13317,10 +13334,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13431,10 +13448,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13460,16 +13477,16 @@
         <v>141</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>77</v>
@@ -13506,7 +13523,7 @@
         <v>77</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="AC96" s="2"/>
       <c r="AD96" t="s" s="2">
@@ -13516,7 +13533,7 @@
         <v>114</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -13534,24 +13551,24 @@
         <v>77</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>359</v>
+        <v>364</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="D97" t="s" s="2">
         <v>77</v>
@@ -13576,16 +13593,16 @@
         <v>141</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>77</v>
@@ -13595,7 +13612,7 @@
         <v>77</v>
       </c>
       <c r="S97" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="T97" t="s" s="2">
         <v>77</v>
@@ -13610,11 +13627,11 @@
         <v>77</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Y97" s="2"/>
       <c r="Z97" t="s" s="2">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>77</v>
@@ -13632,7 +13649,7 @@
         <v>77</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
@@ -13650,21 +13667,21 @@
         <v>77</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>359</v>
+        <v>364</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13773,10 +13790,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13887,10 +13904,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13916,16 +13933,16 @@
         <v>129</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>77</v>
@@ -13974,7 +13991,7 @@
         <v>77</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -13992,21 +14009,21 @@
         <v>77</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14032,13 +14049,13 @@
         <v>101</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14088,7 +14105,7 @@
         <v>77</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -14106,21 +14123,21 @@
         <v>77</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14146,14 +14163,14 @@
         <v>166</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>77</v>
@@ -14202,7 +14219,7 @@
         <v>77</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -14220,21 +14237,21 @@
         <v>77</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14260,16 +14277,16 @@
         <v>101</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>77</v>
@@ -14318,7 +14335,7 @@
         <v>77</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
@@ -14336,21 +14353,21 @@
         <v>77</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14373,19 +14390,19 @@
         <v>88</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>77</v>
@@ -14434,7 +14451,7 @@
         <v>77</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
@@ -14452,21 +14469,21 @@
         <v>77</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14492,16 +14509,16 @@
         <v>101</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>77</v>
@@ -14550,7 +14567,7 @@
         <v>77</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
@@ -14568,21 +14585,21 @@
         <v>77</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>406</v>
+        <v>411</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14605,16 +14622,16 @@
         <v>88</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -14664,7 +14681,7 @@
         <v>77</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
@@ -14676,27 +14693,27 @@
         <v>149</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14805,10 +14822,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14919,10 +14936,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14945,16 +14962,16 @@
         <v>88</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -14984,7 +15001,7 @@
       </c>
       <c r="Y109" s="2"/>
       <c r="Z109" t="s" s="2">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>77</v>
@@ -15002,7 +15019,7 @@
         <v>77</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>78</v>
@@ -15014,27 +15031,27 @@
         <v>149</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>500</v>
+        <v>505</v>
       </c>
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15143,10 +15160,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15257,16 +15274,16 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="D112" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
@@ -15285,15 +15302,17 @@
         <v>77</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="N112" s="2"/>
+        <v>511</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>77</v>
@@ -15351,7 +15370,7 @@
         <v>79</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="AJ112" t="s" s="2">
         <v>116</v>
@@ -15360,7 +15379,7 @@
         <v>77</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>77</v>
@@ -15371,10 +15390,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15483,10 +15502,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15512,10 +15531,10 @@
         <v>108</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -15595,10 +15614,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15624,13 +15643,13 @@
         <v>129</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -15638,7 +15657,7 @@
       </c>
       <c r="Q115" s="2"/>
       <c r="R115" t="s" s="2">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="S115" t="s" s="2">
         <v>77</v>
@@ -15680,7 +15699,7 @@
         <v>77</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>87</v>
@@ -15698,7 +15717,7 @@
         <v>77</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>77</v>
@@ -15709,10 +15728,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15738,10 +15757,10 @@
         <v>101</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -15765,7 +15784,7 @@
         <v>77</v>
       </c>
       <c r="W116" t="s" s="2">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="X116" t="s" s="2">
         <v>77</v>
@@ -15792,7 +15811,7 @@
         <v>77</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>78</v>
@@ -15810,7 +15829,7 @@
         <v>77</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AM116" t="s" s="2">
         <v>77</v>
@@ -15821,16 +15840,16 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="D117" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
@@ -15849,15 +15868,17 @@
         <v>77</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="N117" s="2"/>
+        <v>526</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
         <v>77</v>
@@ -15915,7 +15936,7 @@
         <v>79</v>
       </c>
       <c r="AI117" t="s" s="2">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="AJ117" t="s" s="2">
         <v>116</v>
@@ -15924,7 +15945,7 @@
         <v>77</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>77</v>
@@ -15935,10 +15956,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16047,10 +16068,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16076,10 +16097,10 @@
         <v>108</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -16159,10 +16180,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16188,13 +16209,13 @@
         <v>129</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -16202,7 +16223,7 @@
       </c>
       <c r="Q120" s="2"/>
       <c r="R120" t="s" s="2">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="S120" t="s" s="2">
         <v>77</v>
@@ -16244,7 +16265,7 @@
         <v>77</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>87</v>
@@ -16262,7 +16283,7 @@
         <v>77</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>77</v>
@@ -16273,10 +16294,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16302,10 +16323,10 @@
         <v>101</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -16329,7 +16350,7 @@
         <v>77</v>
       </c>
       <c r="W121" t="s" s="2">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="X121" t="s" s="2">
         <v>77</v>
@@ -16356,7 +16377,7 @@
         <v>77</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>78</v>
@@ -16374,7 +16395,7 @@
         <v>77</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>77</v>
@@ -16385,10 +16406,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16411,19 +16432,19 @@
         <v>88</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>77</v>
@@ -16472,7 +16493,7 @@
         <v>77</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>78</v>
@@ -16481,7 +16502,7 @@
         <v>87</v>
       </c>
       <c r="AI122" t="s" s="2">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="AJ122" t="s" s="2">
         <v>99</v>
@@ -16490,21 +16511,21 @@
         <v>77</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>536</v>
+        <v>541</v>
       </c>
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16530,20 +16551,20 @@
         <v>166</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" t="s" s="2">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q123" t="s" s="2">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="R123" t="s" s="2">
         <v>77</v>
@@ -16564,13 +16585,13 @@
         <v>77</v>
       </c>
       <c r="X123" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Y123" t="s" s="2">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="Z123" t="s" s="2">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="AA123" t="s" s="2">
         <v>77</v>
@@ -16588,7 +16609,7 @@
         <v>77</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>78</v>
@@ -16606,21 +16627,21 @@
         <v>77</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="AM123" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>546</v>
+        <v>551</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16646,16 +16667,16 @@
         <v>101</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>77</v>
@@ -16704,7 +16725,7 @@
         <v>77</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>78</v>
@@ -16722,21 +16743,21 @@
         <v>77</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="AM124" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>553</v>
+        <v>558</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16762,16 +16783,16 @@
         <v>129</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>77</v>
@@ -16820,7 +16841,7 @@
         <v>77</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>78</v>
@@ -16829,7 +16850,7 @@
         <v>87</v>
       </c>
       <c r="AI125" t="s" s="2">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="AJ125" t="s" s="2">
         <v>99</v>
@@ -16838,21 +16859,21 @@
         <v>77</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="AM125" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>553</v>
+        <v>558</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16878,16 +16899,16 @@
         <v>166</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>77</v>
@@ -16936,7 +16957,7 @@
         <v>77</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>78</v>
@@ -16954,21 +16975,21 @@
         <v>77</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="AM126" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>553</v>
+        <v>558</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -16991,16 +17012,16 @@
         <v>88</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
@@ -17030,7 +17051,7 @@
       </c>
       <c r="Y127" s="2"/>
       <c r="Z127" t="s" s="2">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>77</v>
@@ -17048,7 +17069,7 @@
         <v>77</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>78</v>
@@ -17060,27 +17081,27 @@
         <v>149</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="AK127" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>500</v>
+        <v>505</v>
       </c>
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17189,10 +17210,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17303,10 +17324,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17329,19 +17350,19 @@
         <v>88</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>77</v>
@@ -17390,7 +17411,7 @@
         <v>77</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>78</v>
@@ -17399,7 +17420,7 @@
         <v>87</v>
       </c>
       <c r="AI130" t="s" s="2">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="AJ130" t="s" s="2">
         <v>99</v>
@@ -17408,21 +17429,21 @@
         <v>77</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="AM130" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>536</v>
+        <v>541</v>
       </c>
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17448,20 +17469,20 @@
         <v>166</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" t="s" s="2">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q131" t="s" s="2">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="R131" t="s" s="2">
         <v>77</v>
@@ -17482,13 +17503,13 @@
         <v>77</v>
       </c>
       <c r="X131" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Y131" t="s" s="2">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="Z131" t="s" s="2">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>77</v>
@@ -17506,7 +17527,7 @@
         <v>77</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>78</v>
@@ -17524,21 +17545,21 @@
         <v>77</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="AM131" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>546</v>
+        <v>551</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17564,16 +17585,16 @@
         <v>101</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>77</v>
@@ -17622,7 +17643,7 @@
         <v>77</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>78</v>
@@ -17640,21 +17661,21 @@
         <v>77</v>
       </c>
       <c r="AL132" t="s" s="2">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="AM132" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>553</v>
+        <v>558</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17680,16 +17701,16 @@
         <v>129</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="O133" t="s" s="2">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>77</v>
@@ -17738,7 +17759,7 @@
         <v>77</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>78</v>
@@ -17747,7 +17768,7 @@
         <v>87</v>
       </c>
       <c r="AI133" t="s" s="2">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="AJ133" t="s" s="2">
         <v>99</v>
@@ -17756,21 +17777,21 @@
         <v>77</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="AM133" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>553</v>
+        <v>558</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -17796,16 +17817,16 @@
         <v>166</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>77</v>
@@ -17854,7 +17875,7 @@
         <v>77</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>78</v>
@@ -17872,21 +17893,21 @@
         <v>77</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="AM134" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>553</v>
+        <v>558</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -17909,16 +17930,16 @@
         <v>77</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
@@ -17968,7 +17989,7 @@
         <v>77</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>78</v>
@@ -17986,7 +18007,7 @@
         <v>77</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="AM135" t="s" s="2">
         <v>77</v>
@@ -17997,10 +18018,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18109,10 +18130,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18223,16 +18244,16 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="D138" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
@@ -18251,15 +18272,17 @@
         <v>77</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="N138" s="2"/>
+        <v>597</v>
+      </c>
+      <c r="N138" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
         <v>77</v>
@@ -18317,7 +18340,7 @@
         <v>79</v>
       </c>
       <c r="AI138" t="s" s="2">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="AJ138" t="s" s="2">
         <v>116</v>
@@ -18326,7 +18349,7 @@
         <v>77</v>
       </c>
       <c r="AL138" t="s" s="2">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="AM138" t="s" s="2">
         <v>77</v>
@@ -18337,14 +18360,14 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
@@ -18366,16 +18389,16 @@
         <v>108</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="N139" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O139" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>77</v>
@@ -18424,7 +18447,7 @@
         <v>77</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>78</v>
@@ -18442,7 +18465,7 @@
         <v>77</v>
       </c>
       <c r="AL139" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AM139" t="s" s="2">
         <v>77</v>
@@ -18453,10 +18476,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18479,17 +18502,17 @@
         <v>77</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" t="s" s="2">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>77</v>
@@ -18526,17 +18549,17 @@
         <v>77</v>
       </c>
       <c r="AB140" t="s" s="2">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="AC140" s="2"/>
       <c r="AD140" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE140" t="s" s="2">
-        <v>604</v>
+        <v>114</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>87</v>
@@ -18551,27 +18574,27 @@
         <v>99</v>
       </c>
       <c r="AK140" t="s" s="2">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="AL140" t="s" s="2">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="AM140" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>606</v>
+        <v>610</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="C141" t="s" s="2">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="D141" t="s" s="2">
         <v>77</v>
@@ -18593,17 +18616,17 @@
         <v>77</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" t="s" s="2">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>77</v>
@@ -18652,7 +18675,7 @@
         <v>77</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>87</v>
@@ -18667,24 +18690,24 @@
         <v>99</v>
       </c>
       <c r="AK141" t="s" s="2">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="AL141" t="s" s="2">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="AM141" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>606</v>
+        <v>610</v>
       </c>
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -18793,10 +18816,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -18907,10 +18930,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -18936,16 +18959,16 @@
         <v>141</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="O144" t="s" s="2">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>77</v>
@@ -18982,7 +19005,7 @@
         <v>77</v>
       </c>
       <c r="AB144" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="AC144" s="2"/>
       <c r="AD144" t="s" s="2">
@@ -18992,7 +19015,7 @@
         <v>114</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>78</v>
@@ -19010,24 +19033,24 @@
         <v>77</v>
       </c>
       <c r="AL144" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="AM144" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN144" t="s" s="2">
-        <v>359</v>
+        <v>364</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="C145" t="s" s="2">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="D145" t="s" s="2">
         <v>77</v>
@@ -19052,16 +19075,16 @@
         <v>141</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="O145" t="s" s="2">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>77</v>
@@ -19071,7 +19094,7 @@
         <v>77</v>
       </c>
       <c r="S145" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="T145" t="s" s="2">
         <v>77</v>
@@ -19110,7 +19133,7 @@
         <v>77</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>78</v>
@@ -19128,21 +19151,21 @@
         <v>77</v>
       </c>
       <c r="AL145" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="AM145" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN145" t="s" s="2">
-        <v>359</v>
+        <v>364</v>
       </c>
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19251,10 +19274,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19365,10 +19388,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -19394,16 +19417,16 @@
         <v>129</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="O148" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>77</v>
@@ -19452,7 +19475,7 @@
         <v>77</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>78</v>
@@ -19470,21 +19493,21 @@
         <v>77</v>
       </c>
       <c r="AL148" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="AM148" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN148" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -19510,13 +19533,13 @@
         <v>101</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
@@ -19566,7 +19589,7 @@
         <v>77</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>78</v>
@@ -19584,21 +19607,21 @@
         <v>77</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AM149" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -19624,14 +19647,14 @@
         <v>166</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>77</v>
@@ -19680,7 +19703,7 @@
         <v>77</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>78</v>
@@ -19698,21 +19721,21 @@
         <v>77</v>
       </c>
       <c r="AL150" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="AM150" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN150" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -19738,16 +19761,16 @@
         <v>101</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="O151" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>77</v>
@@ -19796,7 +19819,7 @@
         <v>77</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>78</v>
@@ -19814,21 +19837,21 @@
         <v>77</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="AM151" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN151" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -19851,19 +19874,19 @@
         <v>88</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="O152" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>77</v>
@@ -19912,7 +19935,7 @@
         <v>77</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>78</v>
@@ -19930,24 +19953,24 @@
         <v>77</v>
       </c>
       <c r="AL152" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="AM152" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN152" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="C153" t="s" s="2">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="D153" t="s" s="2">
         <v>77</v>
@@ -19972,16 +19995,16 @@
         <v>141</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="O153" t="s" s="2">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>77</v>
@@ -19991,7 +20014,7 @@
         <v>77</v>
       </c>
       <c r="S153" t="s" s="2">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="T153" t="s" s="2">
         <v>77</v>
@@ -20030,7 +20053,7 @@
         <v>77</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>78</v>
@@ -20048,21 +20071,21 @@
         <v>77</v>
       </c>
       <c r="AL153" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="AM153" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN153" t="s" s="2">
-        <v>359</v>
+        <v>364</v>
       </c>
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -20171,10 +20194,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -20285,10 +20308,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -20314,16 +20337,16 @@
         <v>129</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="O156" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>77</v>
@@ -20372,7 +20395,7 @@
         <v>77</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>78</v>
@@ -20390,21 +20413,21 @@
         <v>77</v>
       </c>
       <c r="AL156" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="AM156" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN156" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -20430,13 +20453,13 @@
         <v>101</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
@@ -20486,7 +20509,7 @@
         <v>77</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>78</v>
@@ -20504,21 +20527,21 @@
         <v>77</v>
       </c>
       <c r="AL157" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AM157" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN157" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -20544,14 +20567,14 @@
         <v>166</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>77</v>
@@ -20600,7 +20623,7 @@
         <v>77</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>78</v>
@@ -20618,21 +20641,21 @@
         <v>77</v>
       </c>
       <c r="AL158" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="AM158" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN158" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -20658,16 +20681,16 @@
         <v>101</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="O159" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>77</v>
@@ -20716,7 +20739,7 @@
         <v>77</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>78</v>
@@ -20734,21 +20757,21 @@
         <v>77</v>
       </c>
       <c r="AL159" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="AM159" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN159" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -20771,19 +20794,19 @@
         <v>88</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="O160" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>77</v>
@@ -20832,7 +20855,7 @@
         <v>77</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>78</v>
@@ -20850,24 +20873,24 @@
         <v>77</v>
       </c>
       <c r="AL160" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="AM160" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN160" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="C161" t="s" s="2">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="D161" t="s" s="2">
         <v>77</v>
@@ -20892,16 +20915,16 @@
         <v>141</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="O161" t="s" s="2">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>77</v>
@@ -20911,46 +20934,46 @@
         <v>77</v>
       </c>
       <c r="S161" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="T161" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U161" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V161" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W161" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X161" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y161" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z161" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA161" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB161" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC161" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD161" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE161" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF161" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="T161" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U161" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V161" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W161" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X161" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y161" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z161" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA161" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB161" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC161" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD161" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE161" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF161" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>78</v>
@@ -20968,21 +20991,21 @@
         <v>77</v>
       </c>
       <c r="AL161" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="AM161" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN161" t="s" s="2">
-        <v>359</v>
+        <v>364</v>
       </c>
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -21091,10 +21114,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -21205,10 +21228,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -21234,16 +21257,16 @@
         <v>129</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="O164" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>77</v>
@@ -21292,7 +21315,7 @@
         <v>77</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>78</v>
@@ -21310,21 +21333,21 @@
         <v>77</v>
       </c>
       <c r="AL164" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="AM164" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN164" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -21350,13 +21373,13 @@
         <v>101</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
@@ -21406,7 +21429,7 @@
         <v>77</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>78</v>
@@ -21424,21 +21447,21 @@
         <v>77</v>
       </c>
       <c r="AL165" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AM165" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN165" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -21464,14 +21487,14 @@
         <v>166</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>77</v>
@@ -21520,7 +21543,7 @@
         <v>77</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>78</v>
@@ -21538,21 +21561,21 @@
         <v>77</v>
       </c>
       <c r="AL166" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="AM166" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN166" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -21578,16 +21601,16 @@
         <v>101</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="O167" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>77</v>
@@ -21636,7 +21659,7 @@
         <v>77</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>78</v>
@@ -21654,21 +21677,21 @@
         <v>77</v>
       </c>
       <c r="AL167" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="AM167" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN167" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -21691,19 +21714,19 @@
         <v>88</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="O168" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>77</v>
@@ -21752,7 +21775,7 @@
         <v>77</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>78</v>
@@ -21770,21 +21793,21 @@
         <v>77</v>
       </c>
       <c r="AL168" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="AM168" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN168" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -21810,16 +21833,16 @@
         <v>101</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="O169" t="s" s="2">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>77</v>
@@ -21868,7 +21891,7 @@
         <v>77</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>78</v>
@@ -21886,24 +21909,24 @@
         <v>77</v>
       </c>
       <c r="AL169" t="s" s="2">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="AM169" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN169" t="s" s="2">
-        <v>406</v>
+        <v>411</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="C170" t="s" s="2">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="D170" t="s" s="2">
         <v>77</v>
@@ -21925,17 +21948,17 @@
         <v>77</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="N170" s="2"/>
       <c r="O170" t="s" s="2">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="P170" t="s" s="2">
         <v>77</v>
@@ -21984,7 +22007,7 @@
         <v>77</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>87</v>
@@ -21999,24 +22022,24 @@
         <v>99</v>
       </c>
       <c r="AK170" t="s" s="2">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="AL170" t="s" s="2">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="AM170" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN170" t="s" s="2">
-        <v>606</v>
+        <v>610</v>
       </c>
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -22039,17 +22062,17 @@
         <v>77</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="N171" s="2"/>
       <c r="O171" t="s" s="2">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="P171" t="s" s="2">
         <v>77</v>
@@ -22098,7 +22121,7 @@
         <v>77</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>78</v>
@@ -22116,7 +22139,7 @@
         <v>77</v>
       </c>
       <c r="AL171" t="s" s="2">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="AM171" t="s" s="2">
         <v>77</v>
@@ -22127,10 +22150,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -22153,16 +22176,16 @@
         <v>77</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
@@ -22212,7 +22235,7 @@
         <v>77</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>78</v>
@@ -22224,27 +22247,27 @@
         <v>149</v>
       </c>
       <c r="AJ172" t="s" s="2">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="AK172" t="s" s="2">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="AL172" t="s" s="2">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="AM172" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN172" t="s" s="2">
-        <v>662</v>
+        <v>666</v>
       </c>
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -22353,10 +22376,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -22467,16 +22490,16 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="C175" t="s" s="2">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="D175" t="s" s="2">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="E175" s="2"/>
       <c r="F175" t="s" s="2">
@@ -22495,15 +22518,17 @@
         <v>77</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>668</v>
-      </c>
-      <c r="N175" s="2"/>
+        <v>672</v>
+      </c>
+      <c r="N175" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
         <v>77</v>
@@ -22561,7 +22586,7 @@
         <v>79</v>
       </c>
       <c r="AI175" t="s" s="2">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="AJ175" t="s" s="2">
         <v>116</v>
@@ -22570,7 +22595,7 @@
         <v>77</v>
       </c>
       <c r="AL175" t="s" s="2">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="AM175" t="s" s="2">
         <v>77</v>
@@ -22581,10 +22606,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -22693,10 +22718,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -22722,10 +22747,10 @@
         <v>108</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="N177" s="2"/>
       <c r="O177" s="2"/>
@@ -22805,10 +22830,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -22834,13 +22859,13 @@
         <v>129</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="N178" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="O178" s="2"/>
       <c r="P178" t="s" s="2">
@@ -22848,7 +22873,7 @@
       </c>
       <c r="Q178" s="2"/>
       <c r="R178" t="s" s="2">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="S178" t="s" s="2">
         <v>77</v>
@@ -22890,7 +22915,7 @@
         <v>77</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>87</v>
@@ -22908,7 +22933,7 @@
         <v>77</v>
       </c>
       <c r="AL178" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AM178" t="s" s="2">
         <v>77</v>
@@ -22919,10 +22944,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -22948,10 +22973,10 @@
         <v>101</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="N179" s="2"/>
       <c r="O179" s="2"/>
@@ -22975,7 +23000,7 @@
         <v>77</v>
       </c>
       <c r="W179" t="s" s="2">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="X179" t="s" s="2">
         <v>77</v>
@@ -23002,7 +23027,7 @@
         <v>77</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>78</v>
@@ -23020,7 +23045,7 @@
         <v>77</v>
       </c>
       <c r="AL179" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AM179" t="s" s="2">
         <v>77</v>
@@ -23031,10 +23056,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -23057,16 +23082,16 @@
         <v>88</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="N180" t="s" s="2">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="O180" s="2"/>
       <c r="P180" t="s" s="2">
@@ -23096,7 +23121,7 @@
       </c>
       <c r="Y180" s="2"/>
       <c r="Z180" t="s" s="2">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="AA180" t="s" s="2">
         <v>77</v>
@@ -23114,7 +23139,7 @@
         <v>77</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>78</v>
@@ -23126,27 +23151,27 @@
         <v>149</v>
       </c>
       <c r="AJ180" t="s" s="2">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="AK180" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL180" t="s" s="2">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="AM180" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN180" t="s" s="2">
-        <v>500</v>
+        <v>505</v>
       </c>
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -23255,10 +23280,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -23369,10 +23394,10 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -23395,19 +23420,19 @@
         <v>88</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="N183" t="s" s="2">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="O183" t="s" s="2">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="P183" t="s" s="2">
         <v>77</v>
@@ -23456,7 +23481,7 @@
         <v>77</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>78</v>
@@ -23465,7 +23490,7 @@
         <v>87</v>
       </c>
       <c r="AI183" t="s" s="2">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="AJ183" t="s" s="2">
         <v>99</v>
@@ -23474,21 +23499,21 @@
         <v>77</v>
       </c>
       <c r="AL183" t="s" s="2">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="AM183" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN183" t="s" s="2">
-        <v>536</v>
+        <v>541</v>
       </c>
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -23514,20 +23539,20 @@
         <v>166</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="N184" s="2"/>
       <c r="O184" t="s" s="2">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="P184" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q184" t="s" s="2">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="R184" t="s" s="2">
         <v>77</v>
@@ -23548,13 +23573,13 @@
         <v>77</v>
       </c>
       <c r="X184" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Y184" t="s" s="2">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="Z184" t="s" s="2">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="AA184" t="s" s="2">
         <v>77</v>
@@ -23572,7 +23597,7 @@
         <v>77</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>78</v>
@@ -23590,21 +23615,21 @@
         <v>77</v>
       </c>
       <c r="AL184" t="s" s="2">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="AM184" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN184" t="s" s="2">
-        <v>546</v>
+        <v>551</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -23630,16 +23655,16 @@
         <v>101</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="O185" t="s" s="2">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="P185" t="s" s="2">
         <v>77</v>
@@ -23688,7 +23713,7 @@
         <v>77</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>78</v>
@@ -23706,21 +23731,21 @@
         <v>77</v>
       </c>
       <c r="AL185" t="s" s="2">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="AM185" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN185" t="s" s="2">
-        <v>553</v>
+        <v>558</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -23746,16 +23771,16 @@
         <v>129</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="N186" t="s" s="2">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="O186" t="s" s="2">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="P186" t="s" s="2">
         <v>77</v>
@@ -23804,7 +23829,7 @@
         <v>77</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>78</v>
@@ -23813,7 +23838,7 @@
         <v>87</v>
       </c>
       <c r="AI186" t="s" s="2">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="AJ186" t="s" s="2">
         <v>99</v>
@@ -23822,21 +23847,21 @@
         <v>77</v>
       </c>
       <c r="AL186" t="s" s="2">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="AM186" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN186" t="s" s="2">
-        <v>553</v>
+        <v>558</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -23862,16 +23887,16 @@
         <v>166</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="N187" t="s" s="2">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="O187" t="s" s="2">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>77</v>
@@ -23920,7 +23945,7 @@
         <v>77</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>78</v>
@@ -23938,21 +23963,21 @@
         <v>77</v>
       </c>
       <c r="AL187" t="s" s="2">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="AM187" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN187" t="s" s="2">
-        <v>553</v>
+        <v>558</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -23975,16 +24000,16 @@
         <v>88</v>
       </c>
       <c r="K188" t="s" s="2">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="N188" t="s" s="2">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="O188" s="2"/>
       <c r="P188" t="s" s="2">
@@ -24014,7 +24039,7 @@
       </c>
       <c r="Y188" s="2"/>
       <c r="Z188" t="s" s="2">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="AA188" t="s" s="2">
         <v>77</v>
@@ -24032,7 +24057,7 @@
         <v>77</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>78</v>
@@ -24044,27 +24069,27 @@
         <v>149</v>
       </c>
       <c r="AJ188" t="s" s="2">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="AK188" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL188" t="s" s="2">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="AM188" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN188" t="s" s="2">
-        <v>500</v>
+        <v>505</v>
       </c>
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -24173,10 +24198,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -24287,10 +24312,10 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -24313,19 +24338,19 @@
         <v>88</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="N191" t="s" s="2">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="O191" t="s" s="2">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="P191" t="s" s="2">
         <v>77</v>
@@ -24374,7 +24399,7 @@
         <v>77</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>78</v>
@@ -24383,7 +24408,7 @@
         <v>87</v>
       </c>
       <c r="AI191" t="s" s="2">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="AJ191" t="s" s="2">
         <v>99</v>
@@ -24392,21 +24417,21 @@
         <v>77</v>
       </c>
       <c r="AL191" t="s" s="2">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="AM191" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN191" t="s" s="2">
-        <v>536</v>
+        <v>541</v>
       </c>
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -24432,20 +24457,20 @@
         <v>166</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="N192" s="2"/>
       <c r="O192" t="s" s="2">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="P192" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q192" t="s" s="2">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="R192" t="s" s="2">
         <v>77</v>
@@ -24466,13 +24491,13 @@
         <v>77</v>
       </c>
       <c r="X192" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Y192" t="s" s="2">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="Z192" t="s" s="2">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="AA192" t="s" s="2">
         <v>77</v>
@@ -24490,7 +24515,7 @@
         <v>77</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>78</v>
@@ -24508,21 +24533,21 @@
         <v>77</v>
       </c>
       <c r="AL192" t="s" s="2">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="AM192" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN192" t="s" s="2">
-        <v>546</v>
+        <v>551</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -24548,16 +24573,16 @@
         <v>101</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="N193" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="O193" t="s" s="2">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="P193" t="s" s="2">
         <v>77</v>
@@ -24606,7 +24631,7 @@
         <v>77</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>78</v>
@@ -24624,21 +24649,21 @@
         <v>77</v>
       </c>
       <c r="AL193" t="s" s="2">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="AM193" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN193" t="s" s="2">
-        <v>553</v>
+        <v>558</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -24664,16 +24689,16 @@
         <v>129</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="N194" t="s" s="2">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="O194" t="s" s="2">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="P194" t="s" s="2">
         <v>77</v>
@@ -24722,7 +24747,7 @@
         <v>77</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>78</v>
@@ -24731,7 +24756,7 @@
         <v>87</v>
       </c>
       <c r="AI194" t="s" s="2">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="AJ194" t="s" s="2">
         <v>99</v>
@@ -24740,21 +24765,21 @@
         <v>77</v>
       </c>
       <c r="AL194" t="s" s="2">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="AM194" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN194" t="s" s="2">
-        <v>553</v>
+        <v>558</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -24780,16 +24805,16 @@
         <v>166</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="N195" t="s" s="2">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="O195" t="s" s="2">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="P195" t="s" s="2">
         <v>77</v>
@@ -24838,7 +24863,7 @@
         <v>77</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>78</v>
@@ -24856,21 +24881,21 @@
         <v>77</v>
       </c>
       <c r="AL195" t="s" s="2">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="AM195" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN195" t="s" s="2">
-        <v>553</v>
+        <v>558</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -24893,13 +24918,13 @@
         <v>77</v>
       </c>
       <c r="K196" t="s" s="2">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="N196" s="2"/>
       <c r="O196" s="2"/>
@@ -24950,7 +24975,7 @@
         <v>77</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>78</v>
@@ -24965,10 +24990,10 @@
         <v>99</v>
       </c>
       <c r="AK196" t="s" s="2">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="AL196" t="s" s="2">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="AM196" t="s" s="2">
         <v>77</v>
@@ -24979,10 +25004,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -25091,10 +25116,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -25205,14 +25230,14 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="E199" s="2"/>
       <c r="F199" t="s" s="2">
@@ -25234,16 +25259,16 @@
         <v>108</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="N199" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O199" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="P199" t="s" s="2">
         <v>77</v>
@@ -25292,7 +25317,7 @@
         <v>77</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>78</v>
@@ -25310,7 +25335,7 @@
         <v>77</v>
       </c>
       <c r="AL199" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AM199" t="s" s="2">
         <v>77</v>
@@ -25321,10 +25346,10 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -25350,13 +25375,13 @@
         <v>101</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="N200" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="O200" s="2"/>
       <c r="P200" t="s" s="2">
@@ -25406,7 +25431,7 @@
         <v>77</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>78</v>
@@ -25421,24 +25446,24 @@
         <v>99</v>
       </c>
       <c r="AK200" t="s" s="2">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="AL200" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="AM200" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN200" t="s" s="2">
-        <v>706</v>
+        <v>710</v>
       </c>
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -25461,13 +25486,13 @@
         <v>77</v>
       </c>
       <c r="K201" t="s" s="2">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="N201" s="2"/>
       <c r="O201" s="2"/>
@@ -25518,7 +25543,7 @@
         <v>77</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>78</v>
@@ -25533,16 +25558,16 @@
         <v>99</v>
       </c>
       <c r="AK201" t="s" s="2">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="AL201" t="s" s="2">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="AM201" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN201" t="s" s="2">
-        <v>712</v>
+        <v>716</v>
       </c>
     </row>
   </sheetData>

--- a/tiflow-bfarm/fhir-error-codes/1.0.0-draft/StructureDefinition-erp-tprescription-medication.xlsx
+++ b/tiflow-bfarm/fhir-error-codes/1.0.0-draft/StructureDefinition-erp-tprescription-medication.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7294" uniqueCount="717">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7288" uniqueCount="713">
   <si>
     <t>Property</t>
   </si>
@@ -442,7 +442,7 @@
     <t>Medication.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -480,7 +480,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -514,7 +514,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -557,7 +557,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -592,10 +592,6 @@
     <t>Medication.contained</t>
   </si>
   <si>
-    <t>inline resources
-anonymous resourcescontained resources</t>
-  </si>
-  <si>
     <t xml:space="preserve">Medication {https://gematik.de/fhir/epa-medication/StructureDefinition/epa-medication-pharmaceutical-product|https://gematik.de/fhir/epa-medication/StructureDefinition/epa-medication-pzn-ingredient}
 </t>
   </si>
@@ -603,25 +599,22 @@
     <t>Enthaltene Medikationen</t>
   </si>
   <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
     <t>Im Falle einer Rezeptur oder Kombipackung sind die Bestandteile der Rezeptur, bzw. Kombipackung hier als Medications gelistet.</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
   </si>
   <si>
+    <t>Medication.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
     <t>N/A</t>
-  </si>
-  <si>
-    <t>Medication.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
   </si>
   <si>
     <t>Medication.extension:rxPrescriptionProcessIdentifier</t>
@@ -634,7 +627,7 @@
 </t>
   </si>
   <si>
-    <t>Optional Extensions Element</t>
+    <t>Extension</t>
   </si>
   <si>
     <t>This extension is used to track medication prescription transactions between the E-Rezept-Fachdienst and the ePA. The RxPrescriptionProcessIdentifier is generated by the ePA Medication Service and consists of the PrescriptionId and the authoredOn date of the operation parameters request. It ensures consistent referencing and management of medication-related resources across different systems.</t>
@@ -663,9 +656,6 @@
   </si>
   <si>
     <t>Medication.extension.extension</t>
-  </si>
-  <si>
-    <t>Extension</t>
   </si>
   <si>
     <t>An Extension</t>
@@ -1070,12 +1060,6 @@
 </t>
   </si>
   <si>
-    <t>An identifier intended for computation</t>
-  </si>
-  <si>
-    <t>An identifier - identifies some entity uniquely and unambiguously. Typically this is used for business identifiers.</t>
-  </si>
-  <si>
     <t>&lt;valueIdentifier xmlns="http://hl7.org/fhir"&gt;
   &lt;system value="https://gematik.de/fhir/epa-medication/sid/epa-medication-unique-identifier"/&gt;
 &lt;/valueIdentifier&gt;</t>
@@ -1115,7 +1099,7 @@
     <t>A coded concept that defines the type of a medication.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-codes|4.0.1</t>
   </si>
   <si>
     <t>coding.code = //element(*,MedicationType)/DrugCoded/ProductCode@@ -1335,7 +1319,7 @@
     <t>Medication.manufacturer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1405,7 +1389,7 @@
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
   </si>
   <si>
     <t>Reference.type</t>
@@ -1462,7 +1446,7 @@
     <t>A coded concept defining the form of a medication.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-form-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-form-codes|4.0.1</t>
   </si>
   <si>
     <t>coding.code =  //element(*,DrugCodedType)/FormCode@@ -1912,7 +1896,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(Substance|Medication)</t>
+Reference(Substance|4.0.1|Medication|4.0.1)</t>
   </si>
   <si>
     <t>The actual ingredient or content</t>
@@ -1926,6 +1910,9 @@
   <si>
     <t xml:space="preserve">type:$this}
 </t>
+  </si>
+  <si>
+    <t>closed</t>
   </si>
   <si>
     <t>.player</t>
@@ -2576,7 +2563,7 @@
     <col min="1" max="1" width="64.22265625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="45.42578125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="25.1328125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="18.19140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
@@ -4335,7 +4322,7 @@
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>183</v>
+        <v>77</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -4354,16 +4341,16 @@
         <v>77</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="N16" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4413,7 +4400,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -4428,10 +4415,10 @@
         <v>77</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>189</v>
+        <v>85</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>77</v>
@@ -4442,10 +4429,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4474,7 +4461,7 @@
         <v>109</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="N17" t="s" s="2">
         <v>111</v>
@@ -4527,7 +4514,7 @@
         <v>114</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -4545,7 +4532,7 @@
         <v>77</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>77</v>
@@ -4556,13 +4543,13 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D18" t="s" s="2">
         <v>77</v>
@@ -4584,13 +4571,13 @@
         <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="L18" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4641,7 +4628,7 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -4650,7 +4637,7 @@
         <v>79</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>149</v>
+        <v>77</v>
       </c>
       <c r="AJ18" t="s" s="2">
         <v>116</v>
@@ -4659,7 +4646,7 @@
         <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>189</v>
+        <v>77</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>77</v>
@@ -4670,13 +4657,13 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>77</v>
@@ -4698,13 +4685,13 @@
         <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4755,7 +4742,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -4764,7 +4751,7 @@
         <v>79</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>149</v>
+        <v>77</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>116</v>
@@ -4773,7 +4760,7 @@
         <v>77</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>189</v>
+        <v>77</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>77</v>
@@ -4784,10 +4771,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4896,10 +4883,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4925,10 +4912,10 @@
         <v>108</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -5008,10 +4995,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5037,13 +5024,13 @@
         <v>129</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -5051,7 +5038,7 @@
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>77</v>
@@ -5093,7 +5080,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>87</v>
@@ -5111,7 +5098,7 @@
         <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>77</v>
@@ -5122,10 +5109,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5148,13 +5135,13 @@
         <v>77</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -5205,7 +5192,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -5223,7 +5210,7 @@
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>77</v>
@@ -5234,13 +5221,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>77</v>
@@ -5262,13 +5249,13 @@
         <v>77</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -5319,7 +5306,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -5328,7 +5315,7 @@
         <v>79</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>149</v>
+        <v>77</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>116</v>
@@ -5337,7 +5324,7 @@
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>189</v>
+        <v>77</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>77</v>
@@ -5348,10 +5335,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5460,10 +5447,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5489,10 +5476,10 @@
         <v>108</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5572,10 +5559,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5601,13 +5588,13 @@
         <v>129</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5615,7 +5602,7 @@
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="S27" t="s" s="2">
         <v>77</v>
@@ -5657,7 +5644,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>87</v>
@@ -5675,7 +5662,7 @@
         <v>77</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>77</v>
@@ -5686,10 +5673,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5715,10 +5702,10 @@
         <v>141</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5745,11 +5732,11 @@
         <v>77</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="Y28" s="2"/>
       <c r="Z28" t="s" s="2">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>77</v>
@@ -5767,7 +5754,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5785,7 +5772,7 @@
         <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
@@ -5796,10 +5783,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5908,10 +5895,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6022,10 +6009,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6051,16 +6038,16 @@
         <v>129</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="O31" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>77</v>
@@ -6109,7 +6096,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -6127,21 +6114,21 @@
         <v>77</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6167,13 +6154,13 @@
         <v>101</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6223,7 +6210,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -6241,21 +6228,21 @@
         <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6281,14 +6268,14 @@
         <v>166</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -6337,7 +6324,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -6355,21 +6342,21 @@
         <v>77</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>262</v>
+        <v>259</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6395,16 +6382,16 @@
         <v>101</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="O34" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -6453,7 +6440,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -6471,21 +6458,21 @@
         <v>77</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6508,19 +6495,19 @@
         <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="O35" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -6569,7 +6556,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -6587,27 +6574,27 @@
         <v>77</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="D36" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -6626,17 +6613,15 @@
         <v>77</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -6685,7 +6670,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6694,7 +6679,7 @@
         <v>79</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>149</v>
+        <v>77</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>116</v>
@@ -6703,7 +6688,7 @@
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>105</v>
+        <v>190</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>77</v>
@@ -6714,10 +6699,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6826,10 +6811,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6940,10 +6925,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6969,13 +6954,13 @@
         <v>129</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6983,7 +6968,7 @@
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="S39" t="s" s="2">
         <v>77</v>
@@ -7025,7 +7010,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>87</v>
@@ -7043,7 +7028,7 @@
         <v>77</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>77</v>
@@ -7054,10 +7039,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7083,10 +7068,10 @@
         <v>166</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -7113,11 +7098,11 @@
         <v>77</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>77</v>
@@ -7135,7 +7120,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -7153,7 +7138,7 @@
         <v>77</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>77</v>
@@ -7164,16 +7149,16 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7192,17 +7177,15 @@
         <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>292</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>77</v>
@@ -7251,7 +7234,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -7260,7 +7243,7 @@
         <v>79</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>149</v>
+        <v>77</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>116</v>
@@ -7269,7 +7252,7 @@
         <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>189</v>
+        <v>77</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
@@ -7280,10 +7263,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7392,10 +7375,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7421,10 +7404,10 @@
         <v>108</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7504,10 +7487,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7533,13 +7516,13 @@
         <v>129</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7547,7 +7530,7 @@
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="S44" t="s" s="2">
         <v>77</v>
@@ -7589,7 +7572,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>87</v>
@@ -7607,7 +7590,7 @@
         <v>77</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>77</v>
@@ -7618,10 +7601,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7647,10 +7630,10 @@
         <v>101</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7674,7 +7657,7 @@
         <v>77</v>
       </c>
       <c r="W45" t="s" s="2">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="X45" t="s" s="2">
         <v>77</v>
@@ -7701,7 +7684,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7719,7 +7702,7 @@
         <v>77</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>77</v>
@@ -7730,13 +7713,13 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D46" t="s" s="2">
         <v>77</v>
@@ -7758,13 +7741,13 @@
         <v>77</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7815,7 +7798,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7824,7 +7807,7 @@
         <v>79</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>149</v>
+        <v>77</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>116</v>
@@ -7833,7 +7816,7 @@
         <v>77</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>189</v>
+        <v>77</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>77</v>
@@ -7844,10 +7827,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7956,10 +7939,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7985,10 +7968,10 @@
         <v>108</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -8068,10 +8051,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8097,13 +8080,13 @@
         <v>129</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8111,7 +8094,7 @@
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="S49" t="s" s="2">
         <v>77</v>
@@ -8153,7 +8136,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>87</v>
@@ -8171,7 +8154,7 @@
         <v>77</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>77</v>
@@ -8182,10 +8165,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8211,10 +8194,10 @@
         <v>101</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8238,7 +8221,7 @@
         <v>77</v>
       </c>
       <c r="W50" t="s" s="2">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="X50" t="s" s="2">
         <v>77</v>
@@ -8265,7 +8248,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -8283,7 +8266,7 @@
         <v>77</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>77</v>
@@ -8294,13 +8277,13 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>77</v>
@@ -8322,13 +8305,13 @@
         <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8379,7 +8362,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -8388,7 +8371,7 @@
         <v>79</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>149</v>
+        <v>77</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>116</v>
@@ -8397,7 +8380,7 @@
         <v>77</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>189</v>
+        <v>77</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>77</v>
@@ -8408,10 +8391,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8437,16 +8420,16 @@
         <v>108</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="N52" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -8495,7 +8478,7 @@
         <v>114</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8513,7 +8496,7 @@
         <v>77</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>77</v>
@@ -8524,10 +8507,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8550,16 +8533,16 @@
         <v>88</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="N53" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="L53" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8597,7 +8580,7 @@
         <v>77</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="AC53" s="2"/>
       <c r="AD53" t="s" s="2">
@@ -8607,7 +8590,7 @@
         <v>114</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8625,24 +8608,24 @@
         <v>77</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>333</v>
+        <v>330</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>77</v>
@@ -8664,16 +8647,16 @@
         <v>88</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>337</v>
+        <v>324</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>338</v>
+        <v>325</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8684,7 +8667,7 @@
         <v>77</v>
       </c>
       <c r="S54" t="s" s="2">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="T54" t="s" s="2">
         <v>77</v>
@@ -8723,7 +8706,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8741,24 +8724,24 @@
         <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>333</v>
+        <v>330</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="D55" t="s" s="2">
         <v>77</v>
@@ -8780,16 +8763,16 @@
         <v>88</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>337</v>
+        <v>324</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>338</v>
+        <v>325</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8800,7 +8783,7 @@
         <v>77</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="T55" t="s" s="2">
         <v>77</v>
@@ -8839,7 +8822,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8857,21 +8840,21 @@
         <v>77</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>333</v>
+        <v>330</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8894,16 +8877,16 @@
         <v>88</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8932,10 +8915,10 @@
         <v>156</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>77</v>
@@ -8953,7 +8936,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8968,24 +8951,24 @@
         <v>99</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>354</v>
+        <v>349</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9094,10 +9077,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9208,10 +9191,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9237,16 +9220,16 @@
         <v>141</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>77</v>
@@ -9283,7 +9266,7 @@
         <v>77</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="AC59" s="2"/>
       <c r="AD59" t="s" s="2">
@@ -9293,7 +9276,7 @@
         <v>114</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -9311,24 +9294,24 @@
         <v>77</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>364</v>
+        <v>359</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="D60" t="s" s="2">
         <v>77</v>
@@ -9353,16 +9336,16 @@
         <v>141</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>77</v>
@@ -9372,7 +9355,7 @@
         <v>77</v>
       </c>
       <c r="S60" t="s" s="2">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="T60" t="s" s="2">
         <v>77</v>
@@ -9411,7 +9394,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -9429,21 +9412,21 @@
         <v>77</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>364</v>
+        <v>359</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9552,10 +9535,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9666,10 +9649,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9695,16 +9678,16 @@
         <v>129</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="O63" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>77</v>
@@ -9753,7 +9736,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9771,21 +9754,21 @@
         <v>77</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9811,13 +9794,13 @@
         <v>101</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9867,7 +9850,7 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9885,21 +9868,21 @@
         <v>77</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9925,14 +9908,14 @@
         <v>166</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>77</v>
@@ -9981,7 +9964,7 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9999,21 +9982,21 @@
         <v>77</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>262</v>
+        <v>259</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10039,16 +10022,16 @@
         <v>101</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="O66" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>77</v>
@@ -10097,7 +10080,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -10115,21 +10098,21 @@
         <v>77</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10152,19 +10135,19 @@
         <v>88</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="O67" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>77</v>
@@ -10213,7 +10196,7 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -10231,24 +10214,24 @@
         <v>77</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="D68" t="s" s="2">
         <v>77</v>
@@ -10273,16 +10256,16 @@
         <v>141</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>77</v>
@@ -10292,7 +10275,7 @@
         <v>77</v>
       </c>
       <c r="S68" t="s" s="2">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="T68" t="s" s="2">
         <v>77</v>
@@ -10331,7 +10314,7 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -10349,21 +10332,21 @@
         <v>77</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>364</v>
+        <v>359</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10472,10 +10455,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10586,10 +10569,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10615,16 +10598,16 @@
         <v>129</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="O71" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>77</v>
@@ -10673,7 +10656,7 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10691,21 +10674,21 @@
         <v>77</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10731,13 +10714,13 @@
         <v>101</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10787,7 +10770,7 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10805,21 +10788,21 @@
         <v>77</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10845,14 +10828,14 @@
         <v>166</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>77</v>
@@ -10901,7 +10884,7 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10919,21 +10902,21 @@
         <v>77</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>262</v>
+        <v>259</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10959,16 +10942,16 @@
         <v>101</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="O74" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>77</v>
@@ -11017,7 +11000,7 @@
         <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -11035,21 +11018,21 @@
         <v>77</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11072,19 +11055,19 @@
         <v>88</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="O75" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>77</v>
@@ -11133,7 +11116,7 @@
         <v>77</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -11151,24 +11134,24 @@
         <v>77</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="D76" t="s" s="2">
         <v>77</v>
@@ -11193,16 +11176,16 @@
         <v>141</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>77</v>
@@ -11212,7 +11195,7 @@
         <v>77</v>
       </c>
       <c r="S76" t="s" s="2">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="T76" t="s" s="2">
         <v>77</v>
@@ -11251,7 +11234,7 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -11269,21 +11252,21 @@
         <v>77</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>364</v>
+        <v>359</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11392,10 +11375,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11506,10 +11489,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11535,16 +11518,16 @@
         <v>129</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="O79" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>77</v>
@@ -11593,7 +11576,7 @@
         <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11611,21 +11594,21 @@
         <v>77</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11651,13 +11634,13 @@
         <v>101</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11707,7 +11690,7 @@
         <v>77</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -11725,21 +11708,21 @@
         <v>77</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11765,14 +11748,14 @@
         <v>166</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" t="s" s="2">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>77</v>
@@ -11821,7 +11804,7 @@
         <v>77</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -11839,21 +11822,21 @@
         <v>77</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>262</v>
+        <v>259</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11879,16 +11862,16 @@
         <v>101</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="O82" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>77</v>
@@ -11937,7 +11920,7 @@
         <v>77</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -11955,21 +11938,21 @@
         <v>77</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11992,19 +11975,19 @@
         <v>88</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="O83" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>77</v>
@@ -12053,7 +12036,7 @@
         <v>77</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -12071,21 +12054,21 @@
         <v>77</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12111,16 +12094,16 @@
         <v>101</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>77</v>
@@ -12169,7 +12152,7 @@
         <v>77</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -12187,21 +12170,21 @@
         <v>77</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>411</v>
+        <v>406</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12227,13 +12210,13 @@
         <v>166</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12259,13 +12242,13 @@
         <v>77</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>77</v>
@@ -12283,7 +12266,7 @@
         <v>77</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -12301,7 +12284,7 @@
         <v>77</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>77</v>
@@ -12312,10 +12295,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12338,16 +12321,16 @@
         <v>88</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12397,7 +12380,7 @@
         <v>77</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -12409,27 +12392,27 @@
         <v>149</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>428</v>
+        <v>423</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12538,10 +12521,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12652,10 +12635,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12681,13 +12664,13 @@
         <v>101</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -12737,7 +12720,7 @@
         <v>77</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -12746,7 +12729,7 @@
         <v>87</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="AJ89" t="s" s="2">
         <v>99</v>
@@ -12755,7 +12738,7 @@
         <v>77</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>77</v>
@@ -12766,10 +12749,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12795,13 +12778,13 @@
         <v>129</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -12830,10 +12813,10 @@
         <v>145</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>77</v>
@@ -12851,7 +12834,7 @@
         <v>77</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -12869,7 +12852,7 @@
         <v>77</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>77</v>
@@ -12880,10 +12863,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12906,16 +12889,16 @@
         <v>88</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -12965,7 +12948,7 @@
         <v>77</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -12983,21 +12966,21 @@
         <v>77</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>333</v>
+        <v>330</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13023,13 +13006,13 @@
         <v>101</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13079,7 +13062,7 @@
         <v>77</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -13097,7 +13080,7 @@
         <v>77</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>77</v>
@@ -13108,10 +13091,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13134,16 +13117,16 @@
         <v>77</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13172,10 +13155,10 @@
         <v>156</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>77</v>
@@ -13193,7 +13176,7 @@
         <v>77</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -13208,24 +13191,24 @@
         <v>99</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>463</v>
+        <v>458</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13334,10 +13317,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13448,10 +13431,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13477,16 +13460,16 @@
         <v>141</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>77</v>
@@ -13523,7 +13506,7 @@
         <v>77</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="AC96" s="2"/>
       <c r="AD96" t="s" s="2">
@@ -13533,7 +13516,7 @@
         <v>114</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -13551,24 +13534,24 @@
         <v>77</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>364</v>
+        <v>359</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="D97" t="s" s="2">
         <v>77</v>
@@ -13593,16 +13576,16 @@
         <v>141</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>77</v>
@@ -13612,7 +13595,7 @@
         <v>77</v>
       </c>
       <c r="S97" t="s" s="2">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="T97" t="s" s="2">
         <v>77</v>
@@ -13627,11 +13610,11 @@
         <v>77</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="Y97" s="2"/>
       <c r="Z97" t="s" s="2">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>77</v>
@@ -13649,7 +13632,7 @@
         <v>77</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
@@ -13667,21 +13650,21 @@
         <v>77</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>364</v>
+        <v>359</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13790,10 +13773,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13904,10 +13887,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13933,16 +13916,16 @@
         <v>129</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="O100" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>77</v>
@@ -13991,7 +13974,7 @@
         <v>77</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -14009,21 +13992,21 @@
         <v>77</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14049,13 +14032,13 @@
         <v>101</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -14105,7 +14088,7 @@
         <v>77</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -14123,21 +14106,21 @@
         <v>77</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14163,14 +14146,14 @@
         <v>166</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" t="s" s="2">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>77</v>
@@ -14219,7 +14202,7 @@
         <v>77</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -14237,21 +14220,21 @@
         <v>77</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>262</v>
+        <v>259</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14277,16 +14260,16 @@
         <v>101</v>
       </c>
       <c r="L103" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="O103" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="M103" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>77</v>
@@ -14335,7 +14318,7 @@
         <v>77</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
@@ -14353,21 +14336,21 @@
         <v>77</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14390,19 +14373,19 @@
         <v>88</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="O104" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="M104" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="O104" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>77</v>
@@ -14451,7 +14434,7 @@
         <v>77</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
@@ -14469,21 +14452,21 @@
         <v>77</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14509,16 +14492,16 @@
         <v>101</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>77</v>
@@ -14567,7 +14550,7 @@
         <v>77</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
@@ -14585,21 +14568,21 @@
         <v>77</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>411</v>
+        <v>406</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14622,16 +14605,16 @@
         <v>88</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -14681,7 +14664,7 @@
         <v>77</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
@@ -14693,27 +14676,27 @@
         <v>149</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14822,10 +14805,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14936,10 +14919,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14962,16 +14945,16 @@
         <v>88</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -15001,7 +14984,7 @@
       </c>
       <c r="Y109" s="2"/>
       <c r="Z109" t="s" s="2">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>77</v>
@@ -15019,7 +15002,7 @@
         <v>77</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>78</v>
@@ -15031,27 +15014,27 @@
         <v>149</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>505</v>
+        <v>500</v>
       </c>
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15160,10 +15143,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15274,16 +15257,16 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="D112" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
@@ -15302,17 +15285,15 @@
         <v>77</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>506</v>
+      </c>
+      <c r="N112" s="2"/>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>77</v>
@@ -15370,7 +15351,7 @@
         <v>79</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>149</v>
+        <v>77</v>
       </c>
       <c r="AJ112" t="s" s="2">
         <v>116</v>
@@ -15379,7 +15360,7 @@
         <v>77</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>77</v>
@@ -15390,10 +15371,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15502,10 +15483,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15531,10 +15512,10 @@
         <v>108</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -15614,10 +15595,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15643,13 +15624,13 @@
         <v>129</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -15657,7 +15638,7 @@
       </c>
       <c r="Q115" s="2"/>
       <c r="R115" t="s" s="2">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="S115" t="s" s="2">
         <v>77</v>
@@ -15699,7 +15680,7 @@
         <v>77</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>87</v>
@@ -15717,7 +15698,7 @@
         <v>77</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>77</v>
@@ -15728,10 +15709,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15757,10 +15738,10 @@
         <v>101</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -15784,7 +15765,7 @@
         <v>77</v>
       </c>
       <c r="W116" t="s" s="2">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="X116" t="s" s="2">
         <v>77</v>
@@ -15811,7 +15792,7 @@
         <v>77</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>78</v>
@@ -15829,7 +15810,7 @@
         <v>77</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AM116" t="s" s="2">
         <v>77</v>
@@ -15840,16 +15821,16 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="D117" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
@@ -15868,17 +15849,15 @@
         <v>77</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="N117" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>521</v>
+      </c>
+      <c r="N117" s="2"/>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
         <v>77</v>
@@ -15936,7 +15915,7 @@
         <v>79</v>
       </c>
       <c r="AI117" t="s" s="2">
-        <v>149</v>
+        <v>77</v>
       </c>
       <c r="AJ117" t="s" s="2">
         <v>116</v>
@@ -15945,7 +15924,7 @@
         <v>77</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>77</v>
@@ -15956,10 +15935,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16068,10 +16047,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16097,10 +16076,10 @@
         <v>108</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -16180,10 +16159,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16209,13 +16188,13 @@
         <v>129</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -16223,7 +16202,7 @@
       </c>
       <c r="Q120" s="2"/>
       <c r="R120" t="s" s="2">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="S120" t="s" s="2">
         <v>77</v>
@@ -16265,7 +16244,7 @@
         <v>77</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>87</v>
@@ -16283,7 +16262,7 @@
         <v>77</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>77</v>
@@ -16294,10 +16273,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16323,10 +16302,10 @@
         <v>101</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -16350,7 +16329,7 @@
         <v>77</v>
       </c>
       <c r="W121" t="s" s="2">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="X121" t="s" s="2">
         <v>77</v>
@@ -16377,7 +16356,7 @@
         <v>77</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>78</v>
@@ -16395,7 +16374,7 @@
         <v>77</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>77</v>
@@ -16406,10 +16385,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16432,19 +16411,19 @@
         <v>88</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>77</v>
@@ -16493,7 +16472,7 @@
         <v>77</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>78</v>
@@ -16502,7 +16481,7 @@
         <v>87</v>
       </c>
       <c r="AI122" t="s" s="2">
-        <v>149</v>
+        <v>77</v>
       </c>
       <c r="AJ122" t="s" s="2">
         <v>99</v>
@@ -16511,21 +16490,21 @@
         <v>77</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>541</v>
+        <v>536</v>
       </c>
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16551,20 +16530,20 @@
         <v>166</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" t="s" s="2">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q123" t="s" s="2">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="R123" t="s" s="2">
         <v>77</v>
@@ -16585,13 +16564,13 @@
         <v>77</v>
       </c>
       <c r="X123" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="Y123" t="s" s="2">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="Z123" t="s" s="2">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="AA123" t="s" s="2">
         <v>77</v>
@@ -16609,7 +16588,7 @@
         <v>77</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>78</v>
@@ -16627,21 +16606,21 @@
         <v>77</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="AM123" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>551</v>
+        <v>546</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16667,16 +16646,16 @@
         <v>101</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>77</v>
@@ -16725,7 +16704,7 @@
         <v>77</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>78</v>
@@ -16743,21 +16722,21 @@
         <v>77</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="AM124" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>558</v>
+        <v>553</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16783,16 +16762,16 @@
         <v>129</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>77</v>
@@ -16841,7 +16820,7 @@
         <v>77</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>78</v>
@@ -16850,7 +16829,7 @@
         <v>87</v>
       </c>
       <c r="AI125" t="s" s="2">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="AJ125" t="s" s="2">
         <v>99</v>
@@ -16859,21 +16838,21 @@
         <v>77</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="AM125" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>558</v>
+        <v>553</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16899,16 +16878,16 @@
         <v>166</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>77</v>
@@ -16957,7 +16936,7 @@
         <v>77</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>78</v>
@@ -16975,21 +16954,21 @@
         <v>77</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="AM126" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>558</v>
+        <v>553</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17012,16 +16991,16 @@
         <v>88</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
@@ -17051,7 +17030,7 @@
       </c>
       <c r="Y127" s="2"/>
       <c r="Z127" t="s" s="2">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>77</v>
@@ -17069,7 +17048,7 @@
         <v>77</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>78</v>
@@ -17081,27 +17060,27 @@
         <v>149</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="AK127" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>505</v>
+        <v>500</v>
       </c>
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17210,10 +17189,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17324,10 +17303,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17350,19 +17329,19 @@
         <v>88</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>77</v>
@@ -17411,7 +17390,7 @@
         <v>77</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>78</v>
@@ -17420,7 +17399,7 @@
         <v>87</v>
       </c>
       <c r="AI130" t="s" s="2">
-        <v>149</v>
+        <v>77</v>
       </c>
       <c r="AJ130" t="s" s="2">
         <v>99</v>
@@ -17429,21 +17408,21 @@
         <v>77</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="AM130" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>541</v>
+        <v>536</v>
       </c>
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17469,20 +17448,20 @@
         <v>166</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" t="s" s="2">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q131" t="s" s="2">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="R131" t="s" s="2">
         <v>77</v>
@@ -17503,13 +17482,13 @@
         <v>77</v>
       </c>
       <c r="X131" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="Y131" t="s" s="2">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="Z131" t="s" s="2">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>77</v>
@@ -17527,7 +17506,7 @@
         <v>77</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>78</v>
@@ -17545,21 +17524,21 @@
         <v>77</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="AM131" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>551</v>
+        <v>546</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17585,16 +17564,16 @@
         <v>101</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>77</v>
@@ -17643,7 +17622,7 @@
         <v>77</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>78</v>
@@ -17661,21 +17640,21 @@
         <v>77</v>
       </c>
       <c r="AL132" t="s" s="2">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="AM132" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>558</v>
+        <v>553</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17701,16 +17680,16 @@
         <v>129</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="O133" t="s" s="2">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>77</v>
@@ -17759,7 +17738,7 @@
         <v>77</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>78</v>
@@ -17768,7 +17747,7 @@
         <v>87</v>
       </c>
       <c r="AI133" t="s" s="2">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="AJ133" t="s" s="2">
         <v>99</v>
@@ -17777,21 +17756,21 @@
         <v>77</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="AM133" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>558</v>
+        <v>553</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -17817,16 +17796,16 @@
         <v>166</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>77</v>
@@ -17875,7 +17854,7 @@
         <v>77</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>78</v>
@@ -17893,21 +17872,21 @@
         <v>77</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="AM134" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>558</v>
+        <v>553</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -17930,16 +17909,16 @@
         <v>77</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
@@ -17989,7 +17968,7 @@
         <v>77</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>78</v>
@@ -18007,7 +17986,7 @@
         <v>77</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="AM135" t="s" s="2">
         <v>77</v>
@@ -18018,10 +17997,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18130,10 +18109,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18244,16 +18223,16 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="D138" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
@@ -18272,17 +18251,15 @@
         <v>77</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="N138" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>592</v>
+      </c>
+      <c r="N138" s="2"/>
       <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
         <v>77</v>
@@ -18340,7 +18317,7 @@
         <v>79</v>
       </c>
       <c r="AI138" t="s" s="2">
-        <v>149</v>
+        <v>77</v>
       </c>
       <c r="AJ138" t="s" s="2">
         <v>116</v>
@@ -18349,7 +18326,7 @@
         <v>77</v>
       </c>
       <c r="AL138" t="s" s="2">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="AM138" t="s" s="2">
         <v>77</v>
@@ -18360,14 +18337,14 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
@@ -18389,16 +18366,16 @@
         <v>108</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="N139" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O139" t="s" s="2">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>77</v>
@@ -18447,7 +18424,7 @@
         <v>77</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>78</v>
@@ -18465,7 +18442,7 @@
         <v>77</v>
       </c>
       <c r="AL139" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AM139" t="s" s="2">
         <v>77</v>
@@ -18476,10 +18453,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18502,17 +18479,17 @@
         <v>77</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" t="s" s="2">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>77</v>
@@ -18549,17 +18526,17 @@
         <v>77</v>
       </c>
       <c r="AB140" t="s" s="2">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="AC140" s="2"/>
       <c r="AD140" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE140" t="s" s="2">
-        <v>114</v>
+        <v>604</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>87</v>
@@ -18574,27 +18551,27 @@
         <v>99</v>
       </c>
       <c r="AK140" t="s" s="2">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="AL140" t="s" s="2">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="AM140" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>610</v>
+        <v>606</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="C141" t="s" s="2">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="D141" t="s" s="2">
         <v>77</v>
@@ -18616,17 +18593,17 @@
         <v>77</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" t="s" s="2">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>77</v>
@@ -18675,7 +18652,7 @@
         <v>77</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>87</v>
@@ -18690,24 +18667,24 @@
         <v>99</v>
       </c>
       <c r="AK141" t="s" s="2">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="AL141" t="s" s="2">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="AM141" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>610</v>
+        <v>606</v>
       </c>
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -18816,10 +18793,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -18930,10 +18907,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -18959,16 +18936,16 @@
         <v>141</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="O144" t="s" s="2">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>77</v>
@@ -19005,7 +18982,7 @@
         <v>77</v>
       </c>
       <c r="AB144" t="s" s="2">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="AC144" s="2"/>
       <c r="AD144" t="s" s="2">
@@ -19015,7 +18992,7 @@
         <v>114</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>78</v>
@@ -19033,24 +19010,24 @@
         <v>77</v>
       </c>
       <c r="AL144" t="s" s="2">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="AM144" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN144" t="s" s="2">
-        <v>364</v>
+        <v>359</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="C145" t="s" s="2">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="D145" t="s" s="2">
         <v>77</v>
@@ -19075,16 +19052,16 @@
         <v>141</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="O145" t="s" s="2">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>77</v>
@@ -19094,7 +19071,7 @@
         <v>77</v>
       </c>
       <c r="S145" t="s" s="2">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="T145" t="s" s="2">
         <v>77</v>
@@ -19133,7 +19110,7 @@
         <v>77</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>78</v>
@@ -19151,21 +19128,21 @@
         <v>77</v>
       </c>
       <c r="AL145" t="s" s="2">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="AM145" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN145" t="s" s="2">
-        <v>364</v>
+        <v>359</v>
       </c>
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19274,10 +19251,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19388,10 +19365,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -19417,16 +19394,16 @@
         <v>129</v>
       </c>
       <c r="L148" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="M148" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="N148" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="O148" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="M148" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N148" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="O148" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>77</v>
@@ -19475,7 +19452,7 @@
         <v>77</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>78</v>
@@ -19493,21 +19470,21 @@
         <v>77</v>
       </c>
       <c r="AL148" t="s" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="AM148" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN148" t="s" s="2">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -19533,13 +19510,13 @@
         <v>101</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
@@ -19589,7 +19566,7 @@
         <v>77</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>78</v>
@@ -19607,21 +19584,21 @@
         <v>77</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="AM149" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -19647,14 +19624,14 @@
         <v>166</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" t="s" s="2">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>77</v>
@@ -19703,7 +19680,7 @@
         <v>77</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>78</v>
@@ -19721,21 +19698,21 @@
         <v>77</v>
       </c>
       <c r="AL150" t="s" s="2">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="AM150" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN150" t="s" s="2">
-        <v>262</v>
+        <v>259</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -19761,16 +19738,16 @@
         <v>101</v>
       </c>
       <c r="L151" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="M151" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N151" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="O151" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="M151" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N151" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="O151" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>77</v>
@@ -19819,7 +19796,7 @@
         <v>77</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>78</v>
@@ -19837,21 +19814,21 @@
         <v>77</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="AM151" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN151" t="s" s="2">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -19874,19 +19851,19 @@
         <v>88</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="L152" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M152" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="N152" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="O152" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="M152" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N152" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="O152" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>77</v>
@@ -19935,7 +19912,7 @@
         <v>77</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>78</v>
@@ -19953,24 +19930,24 @@
         <v>77</v>
       </c>
       <c r="AL152" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="AM152" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN152" t="s" s="2">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="C153" t="s" s="2">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="D153" t="s" s="2">
         <v>77</v>
@@ -19995,16 +19972,16 @@
         <v>141</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="O153" t="s" s="2">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>77</v>
@@ -20014,7 +19991,7 @@
         <v>77</v>
       </c>
       <c r="S153" t="s" s="2">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="T153" t="s" s="2">
         <v>77</v>
@@ -20053,7 +20030,7 @@
         <v>77</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>78</v>
@@ -20071,21 +20048,21 @@
         <v>77</v>
       </c>
       <c r="AL153" t="s" s="2">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="AM153" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN153" t="s" s="2">
-        <v>364</v>
+        <v>359</v>
       </c>
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -20194,10 +20171,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -20308,10 +20285,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -20337,16 +20314,16 @@
         <v>129</v>
       </c>
       <c r="L156" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="M156" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="N156" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="O156" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="M156" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N156" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="O156" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>77</v>
@@ -20395,7 +20372,7 @@
         <v>77</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>78</v>
@@ -20413,21 +20390,21 @@
         <v>77</v>
       </c>
       <c r="AL156" t="s" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="AM156" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN156" t="s" s="2">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -20453,13 +20430,13 @@
         <v>101</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
@@ -20509,7 +20486,7 @@
         <v>77</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>78</v>
@@ -20527,21 +20504,21 @@
         <v>77</v>
       </c>
       <c r="AL157" t="s" s="2">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="AM157" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN157" t="s" s="2">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -20567,14 +20544,14 @@
         <v>166</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" t="s" s="2">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>77</v>
@@ -20623,7 +20600,7 @@
         <v>77</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>78</v>
@@ -20641,21 +20618,21 @@
         <v>77</v>
       </c>
       <c r="AL158" t="s" s="2">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="AM158" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN158" t="s" s="2">
-        <v>262</v>
+        <v>259</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -20681,16 +20658,16 @@
         <v>101</v>
       </c>
       <c r="L159" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="M159" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N159" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="O159" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="M159" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N159" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="O159" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>77</v>
@@ -20739,7 +20716,7 @@
         <v>77</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>78</v>
@@ -20757,21 +20734,21 @@
         <v>77</v>
       </c>
       <c r="AL159" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="AM159" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN159" t="s" s="2">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -20794,19 +20771,19 @@
         <v>88</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="L160" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M160" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="N160" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="O160" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="M160" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N160" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="O160" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>77</v>
@@ -20855,7 +20832,7 @@
         <v>77</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>78</v>
@@ -20873,24 +20850,24 @@
         <v>77</v>
       </c>
       <c r="AL160" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="AM160" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN160" t="s" s="2">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="C161" t="s" s="2">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="D161" t="s" s="2">
         <v>77</v>
@@ -20915,16 +20892,16 @@
         <v>141</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="O161" t="s" s="2">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>77</v>
@@ -20934,7 +20911,7 @@
         <v>77</v>
       </c>
       <c r="S161" t="s" s="2">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="T161" t="s" s="2">
         <v>77</v>
@@ -20973,7 +20950,7 @@
         <v>77</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>78</v>
@@ -20991,21 +20968,21 @@
         <v>77</v>
       </c>
       <c r="AL161" t="s" s="2">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="AM161" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN161" t="s" s="2">
-        <v>364</v>
+        <v>359</v>
       </c>
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -21114,10 +21091,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -21228,10 +21205,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -21257,16 +21234,16 @@
         <v>129</v>
       </c>
       <c r="L164" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="M164" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="N164" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="O164" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="M164" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N164" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="O164" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>77</v>
@@ -21315,7 +21292,7 @@
         <v>77</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>78</v>
@@ -21333,21 +21310,21 @@
         <v>77</v>
       </c>
       <c r="AL164" t="s" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="AM164" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN164" t="s" s="2">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -21373,13 +21350,13 @@
         <v>101</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
@@ -21429,7 +21406,7 @@
         <v>77</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>78</v>
@@ -21447,21 +21424,21 @@
         <v>77</v>
       </c>
       <c r="AL165" t="s" s="2">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="AM165" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN165" t="s" s="2">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -21487,14 +21464,14 @@
         <v>166</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" t="s" s="2">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>77</v>
@@ -21543,7 +21520,7 @@
         <v>77</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>78</v>
@@ -21561,21 +21538,21 @@
         <v>77</v>
       </c>
       <c r="AL166" t="s" s="2">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="AM166" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN166" t="s" s="2">
-        <v>262</v>
+        <v>259</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -21601,16 +21578,16 @@
         <v>101</v>
       </c>
       <c r="L167" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="M167" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N167" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="O167" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="M167" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N167" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="O167" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>77</v>
@@ -21659,7 +21636,7 @@
         <v>77</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>78</v>
@@ -21677,21 +21654,21 @@
         <v>77</v>
       </c>
       <c r="AL167" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="AM167" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN167" t="s" s="2">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -21714,19 +21691,19 @@
         <v>88</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="L168" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M168" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="N168" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="O168" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="M168" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N168" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="O168" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>77</v>
@@ -21775,7 +21752,7 @@
         <v>77</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>78</v>
@@ -21793,21 +21770,21 @@
         <v>77</v>
       </c>
       <c r="AL168" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="AM168" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN168" t="s" s="2">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -21833,16 +21810,16 @@
         <v>101</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="O169" t="s" s="2">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>77</v>
@@ -21891,7 +21868,7 @@
         <v>77</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>78</v>
@@ -21909,24 +21886,24 @@
         <v>77</v>
       </c>
       <c r="AL169" t="s" s="2">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="AM169" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN169" t="s" s="2">
-        <v>411</v>
+        <v>406</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="C170" t="s" s="2">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="D170" t="s" s="2">
         <v>77</v>
@@ -21948,17 +21925,17 @@
         <v>77</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="N170" s="2"/>
       <c r="O170" t="s" s="2">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="P170" t="s" s="2">
         <v>77</v>
@@ -22007,7 +21984,7 @@
         <v>77</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>87</v>
@@ -22022,24 +21999,24 @@
         <v>99</v>
       </c>
       <c r="AK170" t="s" s="2">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="AL170" t="s" s="2">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="AM170" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN170" t="s" s="2">
-        <v>610</v>
+        <v>606</v>
       </c>
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -22062,17 +22039,17 @@
         <v>77</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="N171" s="2"/>
       <c r="O171" t="s" s="2">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="P171" t="s" s="2">
         <v>77</v>
@@ -22121,7 +22098,7 @@
         <v>77</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>78</v>
@@ -22139,7 +22116,7 @@
         <v>77</v>
       </c>
       <c r="AL171" t="s" s="2">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="AM171" t="s" s="2">
         <v>77</v>
@@ -22150,10 +22127,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -22176,16 +22153,16 @@
         <v>77</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
@@ -22235,7 +22212,7 @@
         <v>77</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>78</v>
@@ -22247,27 +22224,27 @@
         <v>149</v>
       </c>
       <c r="AJ172" t="s" s="2">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="AK172" t="s" s="2">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="AL172" t="s" s="2">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="AM172" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN172" t="s" s="2">
-        <v>666</v>
+        <v>662</v>
       </c>
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -22376,10 +22353,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -22490,16 +22467,16 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="C175" t="s" s="2">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="D175" t="s" s="2">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="E175" s="2"/>
       <c r="F175" t="s" s="2">
@@ -22518,17 +22495,15 @@
         <v>77</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>672</v>
-      </c>
-      <c r="N175" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>668</v>
+      </c>
+      <c r="N175" s="2"/>
       <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
         <v>77</v>
@@ -22586,7 +22561,7 @@
         <v>79</v>
       </c>
       <c r="AI175" t="s" s="2">
-        <v>149</v>
+        <v>77</v>
       </c>
       <c r="AJ175" t="s" s="2">
         <v>116</v>
@@ -22595,7 +22570,7 @@
         <v>77</v>
       </c>
       <c r="AL175" t="s" s="2">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="AM175" t="s" s="2">
         <v>77</v>
@@ -22606,10 +22581,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -22718,10 +22693,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -22747,10 +22722,10 @@
         <v>108</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="N177" s="2"/>
       <c r="O177" s="2"/>
@@ -22830,10 +22805,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -22859,13 +22834,13 @@
         <v>129</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="N178" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="O178" s="2"/>
       <c r="P178" t="s" s="2">
@@ -22873,7 +22848,7 @@
       </c>
       <c r="Q178" s="2"/>
       <c r="R178" t="s" s="2">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="S178" t="s" s="2">
         <v>77</v>
@@ -22915,7 +22890,7 @@
         <v>77</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>87</v>
@@ -22933,7 +22908,7 @@
         <v>77</v>
       </c>
       <c r="AL178" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AM178" t="s" s="2">
         <v>77</v>
@@ -22944,10 +22919,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -22973,10 +22948,10 @@
         <v>101</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="N179" s="2"/>
       <c r="O179" s="2"/>
@@ -23000,7 +22975,7 @@
         <v>77</v>
       </c>
       <c r="W179" t="s" s="2">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="X179" t="s" s="2">
         <v>77</v>
@@ -23027,7 +23002,7 @@
         <v>77</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>78</v>
@@ -23045,7 +23020,7 @@
         <v>77</v>
       </c>
       <c r="AL179" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AM179" t="s" s="2">
         <v>77</v>
@@ -23056,10 +23031,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -23082,16 +23057,16 @@
         <v>88</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="N180" t="s" s="2">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="O180" s="2"/>
       <c r="P180" t="s" s="2">
@@ -23121,7 +23096,7 @@
       </c>
       <c r="Y180" s="2"/>
       <c r="Z180" t="s" s="2">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="AA180" t="s" s="2">
         <v>77</v>
@@ -23139,7 +23114,7 @@
         <v>77</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>78</v>
@@ -23151,27 +23126,27 @@
         <v>149</v>
       </c>
       <c r="AJ180" t="s" s="2">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="AK180" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL180" t="s" s="2">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="AM180" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN180" t="s" s="2">
-        <v>505</v>
+        <v>500</v>
       </c>
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -23280,10 +23255,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -23394,10 +23369,10 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -23420,19 +23395,19 @@
         <v>88</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="N183" t="s" s="2">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="O183" t="s" s="2">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="P183" t="s" s="2">
         <v>77</v>
@@ -23481,7 +23456,7 @@
         <v>77</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>78</v>
@@ -23490,7 +23465,7 @@
         <v>87</v>
       </c>
       <c r="AI183" t="s" s="2">
-        <v>149</v>
+        <v>77</v>
       </c>
       <c r="AJ183" t="s" s="2">
         <v>99</v>
@@ -23499,21 +23474,21 @@
         <v>77</v>
       </c>
       <c r="AL183" t="s" s="2">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="AM183" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN183" t="s" s="2">
-        <v>541</v>
+        <v>536</v>
       </c>
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -23539,20 +23514,20 @@
         <v>166</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="N184" s="2"/>
       <c r="O184" t="s" s="2">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="P184" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q184" t="s" s="2">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="R184" t="s" s="2">
         <v>77</v>
@@ -23573,13 +23548,13 @@
         <v>77</v>
       </c>
       <c r="X184" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="Y184" t="s" s="2">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="Z184" t="s" s="2">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="AA184" t="s" s="2">
         <v>77</v>
@@ -23597,7 +23572,7 @@
         <v>77</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>78</v>
@@ -23615,21 +23590,21 @@
         <v>77</v>
       </c>
       <c r="AL184" t="s" s="2">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="AM184" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN184" t="s" s="2">
-        <v>551</v>
+        <v>546</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -23655,16 +23630,16 @@
         <v>101</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="O185" t="s" s="2">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="P185" t="s" s="2">
         <v>77</v>
@@ -23713,7 +23688,7 @@
         <v>77</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>78</v>
@@ -23731,21 +23706,21 @@
         <v>77</v>
       </c>
       <c r="AL185" t="s" s="2">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="AM185" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN185" t="s" s="2">
-        <v>558</v>
+        <v>553</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -23771,16 +23746,16 @@
         <v>129</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="N186" t="s" s="2">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="O186" t="s" s="2">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="P186" t="s" s="2">
         <v>77</v>
@@ -23829,7 +23804,7 @@
         <v>77</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>78</v>
@@ -23838,7 +23813,7 @@
         <v>87</v>
       </c>
       <c r="AI186" t="s" s="2">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="AJ186" t="s" s="2">
         <v>99</v>
@@ -23847,21 +23822,21 @@
         <v>77</v>
       </c>
       <c r="AL186" t="s" s="2">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="AM186" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN186" t="s" s="2">
-        <v>558</v>
+        <v>553</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -23887,16 +23862,16 @@
         <v>166</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="N187" t="s" s="2">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="O187" t="s" s="2">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>77</v>
@@ -23945,7 +23920,7 @@
         <v>77</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>78</v>
@@ -23963,21 +23938,21 @@
         <v>77</v>
       </c>
       <c r="AL187" t="s" s="2">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="AM187" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN187" t="s" s="2">
-        <v>558</v>
+        <v>553</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -24000,16 +23975,16 @@
         <v>88</v>
       </c>
       <c r="K188" t="s" s="2">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="N188" t="s" s="2">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="O188" s="2"/>
       <c r="P188" t="s" s="2">
@@ -24039,7 +24014,7 @@
       </c>
       <c r="Y188" s="2"/>
       <c r="Z188" t="s" s="2">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="AA188" t="s" s="2">
         <v>77</v>
@@ -24057,7 +24032,7 @@
         <v>77</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>78</v>
@@ -24069,27 +24044,27 @@
         <v>149</v>
       </c>
       <c r="AJ188" t="s" s="2">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="AK188" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL188" t="s" s="2">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="AM188" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN188" t="s" s="2">
-        <v>505</v>
+        <v>500</v>
       </c>
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -24198,10 +24173,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -24312,10 +24287,10 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -24338,19 +24313,19 @@
         <v>88</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="N191" t="s" s="2">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="O191" t="s" s="2">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="P191" t="s" s="2">
         <v>77</v>
@@ -24399,7 +24374,7 @@
         <v>77</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>78</v>
@@ -24408,7 +24383,7 @@
         <v>87</v>
       </c>
       <c r="AI191" t="s" s="2">
-        <v>149</v>
+        <v>77</v>
       </c>
       <c r="AJ191" t="s" s="2">
         <v>99</v>
@@ -24417,21 +24392,21 @@
         <v>77</v>
       </c>
       <c r="AL191" t="s" s="2">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="AM191" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN191" t="s" s="2">
-        <v>541</v>
+        <v>536</v>
       </c>
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -24457,20 +24432,20 @@
         <v>166</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="N192" s="2"/>
       <c r="O192" t="s" s="2">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="P192" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q192" t="s" s="2">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="R192" t="s" s="2">
         <v>77</v>
@@ -24491,13 +24466,13 @@
         <v>77</v>
       </c>
       <c r="X192" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="Y192" t="s" s="2">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="Z192" t="s" s="2">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="AA192" t="s" s="2">
         <v>77</v>
@@ -24515,7 +24490,7 @@
         <v>77</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>78</v>
@@ -24533,21 +24508,21 @@
         <v>77</v>
       </c>
       <c r="AL192" t="s" s="2">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="AM192" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN192" t="s" s="2">
-        <v>551</v>
+        <v>546</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -24573,16 +24548,16 @@
         <v>101</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="N193" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="O193" t="s" s="2">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="P193" t="s" s="2">
         <v>77</v>
@@ -24631,7 +24606,7 @@
         <v>77</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>78</v>
@@ -24649,21 +24624,21 @@
         <v>77</v>
       </c>
       <c r="AL193" t="s" s="2">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="AM193" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN193" t="s" s="2">
-        <v>558</v>
+        <v>553</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -24689,16 +24664,16 @@
         <v>129</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="N194" t="s" s="2">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="O194" t="s" s="2">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="P194" t="s" s="2">
         <v>77</v>
@@ -24747,7 +24722,7 @@
         <v>77</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>78</v>
@@ -24756,7 +24731,7 @@
         <v>87</v>
       </c>
       <c r="AI194" t="s" s="2">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="AJ194" t="s" s="2">
         <v>99</v>
@@ -24765,21 +24740,21 @@
         <v>77</v>
       </c>
       <c r="AL194" t="s" s="2">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="AM194" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN194" t="s" s="2">
-        <v>558</v>
+        <v>553</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -24805,16 +24780,16 @@
         <v>166</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="N195" t="s" s="2">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="O195" t="s" s="2">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="P195" t="s" s="2">
         <v>77</v>
@@ -24863,7 +24838,7 @@
         <v>77</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>78</v>
@@ -24881,21 +24856,21 @@
         <v>77</v>
       </c>
       <c r="AL195" t="s" s="2">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="AM195" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN195" t="s" s="2">
-        <v>558</v>
+        <v>553</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -24918,13 +24893,13 @@
         <v>77</v>
       </c>
       <c r="K196" t="s" s="2">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="N196" s="2"/>
       <c r="O196" s="2"/>
@@ -24975,7 +24950,7 @@
         <v>77</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>78</v>
@@ -24990,10 +24965,10 @@
         <v>99</v>
       </c>
       <c r="AK196" t="s" s="2">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="AL196" t="s" s="2">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="AM196" t="s" s="2">
         <v>77</v>
@@ -25004,10 +24979,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -25116,10 +25091,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -25230,14 +25205,14 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="E199" s="2"/>
       <c r="F199" t="s" s="2">
@@ -25259,16 +25234,16 @@
         <v>108</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="N199" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O199" t="s" s="2">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="P199" t="s" s="2">
         <v>77</v>
@@ -25317,7 +25292,7 @@
         <v>77</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>78</v>
@@ -25335,7 +25310,7 @@
         <v>77</v>
       </c>
       <c r="AL199" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AM199" t="s" s="2">
         <v>77</v>
@@ -25346,10 +25321,10 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -25375,13 +25350,13 @@
         <v>101</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="N200" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="O200" s="2"/>
       <c r="P200" t="s" s="2">
@@ -25431,7 +25406,7 @@
         <v>77</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>78</v>
@@ -25446,24 +25421,24 @@
         <v>99</v>
       </c>
       <c r="AK200" t="s" s="2">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="AL200" t="s" s="2">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="AM200" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN200" t="s" s="2">
-        <v>710</v>
+        <v>706</v>
       </c>
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -25486,13 +25461,13 @@
         <v>77</v>
       </c>
       <c r="K201" t="s" s="2">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="N201" s="2"/>
       <c r="O201" s="2"/>
@@ -25543,7 +25518,7 @@
         <v>77</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>78</v>
@@ -25558,16 +25533,16 @@
         <v>99</v>
       </c>
       <c r="AK201" t="s" s="2">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="AL201" t="s" s="2">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="AM201" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN201" t="s" s="2">
-        <v>716</v>
+        <v>712</v>
       </c>
     </row>
   </sheetData>
